--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,13 +58,8 @@
       <b val="1"/>
       <color rgb="000070C0"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -96,11 +91,6 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -128,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,10 +157,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +548,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-22 ~ 2026-10-29  (최근 5거래일)  ·  캡처 6/10  ·  대기: RISE, TIGER, TIGER, MIDAS</t>
+          <t>최근 5거래일 변화  ·  2026-10-22 ~ 2026-10-29  (최근 5거래일)  ·  캡처 10/10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,313억   ·   현금 -7억(-0.1%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 9종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,566억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +651,7 @@
         <v>314</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2631610152</v>
+        <v>2634257609</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +672,7 @@
         <v>-82</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-5170553499</v>
+        <v>-5175755188</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +695,7 @@
         <v>224</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4737803890</v>
+        <v>4742570224</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +716,7 @@
         <v>-72</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-643464311</v>
+        <v>-644111650</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +739,7 @@
         <v>170</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4152728007</v>
+        <v>4156905742</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +760,7 @@
         <v>-69</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3059285529</v>
+        <v>-3062363236</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +783,7 @@
         <v>76</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2030090181</v>
+        <v>2032132496</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +804,7 @@
         <v>-46</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2066930499</v>
+        <v>-2069009876</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +827,7 @@
         <v>71</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>5971606987</v>
+        <v>5977614553</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +848,7 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-940470755</v>
+        <v>-941416889</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +871,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>856562214</v>
+        <v>857423934</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +892,7 @@
         <v>-16</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-4369202112</v>
+        <v>-4373597624</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +915,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1305795631</v>
+        <v>1307109290</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +936,7 @@
         <v>-11</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1812126576</v>
+        <v>-1813949615</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +959,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1022790494</v>
+        <v>1023819444</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +980,7 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-117372657</v>
+        <v>-117490736</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1003,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2051042491</v>
+        <v>2053105885</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1024,7 @@
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1017825492</v>
+        <v>-1018849446</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1052,7 @@
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-873840422</v>
+        <v>-874719525</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1082,7 +1068,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,932억   ·   현금 74억(2.5%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 9종목  /  매도 15종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,983억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 9종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1178,7 +1164,7 @@
         <v>141</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2869673552</v>
+        <v>2869674193</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1199,7 +1185,7 @@
         <v>-118</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1482764013</v>
+        <v>-1482764345</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1222,7 +1208,7 @@
         <v>104</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>4317049275</v>
+        <v>4317050239</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1243,7 +1229,7 @@
         <v>-113</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2603214221</v>
+        <v>-2603214803</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1266,7 +1252,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3028679210</v>
+        <v>3028679887</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1287,7 +1273,7 @@
         <v>-58</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1199120687</v>
+        <v>-1199120955</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1310,7 +1296,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1459028620</v>
+        <v>1459028946</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1331,7 +1317,7 @@
         <v>-46</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-5644405528</v>
+        <v>-5644406790</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1354,7 +1340,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>4563693310</v>
+        <v>4563694330</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1375,7 +1361,7 @@
         <v>-43</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-5149291658</v>
+        <v>-5149292808</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1398,7 +1384,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>911020262</v>
+        <v>911020466</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1419,7 +1405,7 @@
         <v>-38</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1985503282</v>
+        <v>-1985503726</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1442,7 +1428,7 @@
         <v>9</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>917303161</v>
+        <v>917303366</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1463,7 +1449,7 @@
         <v>-33</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1173129894</v>
+        <v>-1173130156</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1486,7 +1472,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>149500761</v>
+        <v>149500794</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1507,7 +1493,7 @@
         <v>-32</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-3118895187</v>
+        <v>-3118895884</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1530,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2947055232</v>
+        <v>2947055890</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1551,7 +1537,7 @@
         <v>-26</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-173128755</v>
+        <v>-173128794</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1579,7 +1565,7 @@
         <v>-25</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-283267426</v>
+        <v>-283267489</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1607,7 +1593,7 @@
         <v>-24</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-472345077</v>
+        <v>-472345182</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1635,7 +1621,7 @@
         <v>-22</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-912040562</v>
+        <v>-912040766</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1663,7 +1649,7 @@
         <v>-18</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-144023362</v>
+        <v>-144023395</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1691,7 +1677,7 @@
         <v>-6</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-26452613</v>
+        <v>-26452619</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1719,7 +1705,7 @@
         <v>-4</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-62936384</v>
+        <v>-62936398</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1735,7 +1721,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,112억   ·   현금 45억(2.0%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 20종목  /  매도 25종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,229억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 20종목  /  매도 25종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1831,7 +1817,7 @@
         <v>495</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>3173547801</v>
+        <v>3192696507</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1852,7 +1838,7 @@
         <v>-250</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-6207335253</v>
+        <v>-6244789372</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1875,7 +1861,7 @@
         <v>251</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>4659562313</v>
+        <v>4687677406</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1896,7 +1882,7 @@
         <v>-249</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-7808612273</v>
+        <v>-7855728256</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1919,7 +1905,7 @@
         <v>248</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>6141234177</v>
+        <v>6178289453</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1940,7 +1926,7 @@
         <v>-202</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1049979460</v>
+        <v>-1056314877</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1963,7 +1949,7 @@
         <v>194</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>5273500091</v>
+        <v>5305319591</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1970,7 @@
         <v>-120</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1115430796</v>
+        <v>-1122161136</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2007,7 +1993,7 @@
         <v>138</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2282774474</v>
+        <v>2296548389</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2028,7 +2014,7 @@
         <v>-118</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1090581565</v>
+        <v>-1097161969</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2051,7 +2037,7 @@
         <v>100</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>4137118502</v>
+        <v>4162081248</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2072,7 +2058,7 @@
         <v>-111</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2222507795</v>
+        <v>-2235918070</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2095,7 +2081,7 @@
         <v>99</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1654051801</v>
+        <v>1664032099</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2116,7 +2102,7 @@
         <v>-100</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1886234317</v>
+        <v>-1897615569</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2139,7 +2125,7 @@
         <v>79</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>5719566330</v>
+        <v>5754077325</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2160,7 +2146,7 @@
         <v>-97</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1646361004</v>
+        <v>-1656294897</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2183,7 +2169,7 @@
         <v>70</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2311217163</v>
+        <v>2325162697</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2204,7 +2190,7 @@
         <v>-77</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-9469957072</v>
+        <v>-9527097357</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2227,7 +2213,7 @@
         <v>69</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4066906828</v>
+        <v>4091445927</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2248,7 +2234,7 @@
         <v>-75</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-3455886249</v>
+        <v>-3476738542</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2271,7 +2257,7 @@
         <v>64</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>3420017962</v>
+        <v>3440653832</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2285,23 +2271,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-66</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-5202824317</v>
+        <v>-2005202701</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>3.09%→0.87%</t>
+          <t>1.49%→0.68%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>90→24</t>
+          <t>115→49</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2301,7 @@
         <v>51</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>2231657192</v>
+        <v>2245122673</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2329,23 +2315,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-66</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1993176178</v>
+        <v>-5234217369</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.49%→0.68%</t>
+          <t>3.09%→0.87%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>115→49</t>
+          <t>90→24</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2345,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>831666899</v>
+        <v>836685051</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2380,7 +2366,7 @@
         <v>-59</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-7549578267</v>
+        <v>-7595131277</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2403,7 +2389,7 @@
         <v>41</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>2302399267</v>
+        <v>2316291595</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2424,7 +2410,7 @@
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-815489705</v>
+        <v>-820410246</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2447,7 +2433,7 @@
         <v>38</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2451375313</v>
+        <v>2466166539</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2468,7 +2454,7 @@
         <v>-50</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-3497323734</v>
+        <v>-3518426055</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2491,7 +2477,7 @@
         <v>35</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>6392975186</v>
+        <v>6431549428</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2512,7 +2498,7 @@
         <v>-49</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-2069421151</v>
+        <v>-2081907724</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2535,7 +2521,7 @@
         <v>30</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>4435468394</v>
+        <v>4462231338</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2556,7 +2542,7 @@
         <v>-40</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-2638739045</v>
+        <v>-2654660796</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2579,7 +2565,7 @@
         <v>29</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>2078437948</v>
+        <v>2090978927</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2600,7 +2586,7 @@
         <v>-28</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-2142284825</v>
+        <v>-2155211046</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2623,7 +2609,7 @@
         <v>27</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>744681330</v>
+        <v>749174625</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2644,7 +2630,7 @@
         <v>-27</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-934431862</v>
+        <v>-940070082</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2667,7 +2653,7 @@
         <v>14</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2552549076</v>
+        <v>2567950770</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2681,23 +2667,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1097264603</v>
+        <v>-1629147988</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.71%</t>
+          <t>1.58%→0.75%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2695,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1619376914</v>
+        <v>-1103885331</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.58%→0.75%</t>
+          <t>1.22%→0.71%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2730,7 @@
         <v>-21</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-1775181857</v>
+        <v>-1785893035</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2765,23 +2751,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스  (편출)</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-3161845855</v>
+        <v>-5303652090</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.36%→0.00%</t>
+          <t>3.68%→1.41%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -2793,23 +2779,23 @@
       <c r="E62" s="17" t="n"/>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>파크시스템스  (편출)</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-5271842592</v>
+        <v>-3180923954</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>3.68%→1.41%</t>
+          <t>1.36%→0.00%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2814,7 @@
         <v>-7</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-1225223556</v>
+        <v>-1232616370</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2844,7 +2830,7 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,032억   ·   현금 7억(0.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,074억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B65" s="4" t="n"/>
@@ -2940,7 +2926,7 @@
         <v>138</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>2433574318</v>
+        <v>2427551582</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2961,7 +2947,7 @@
         <v>-291</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-4455674718</v>
+        <v>-4444647582</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -2984,7 +2970,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>986931405</v>
+        <v>984488895</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
         <v>-157</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-1496900504</v>
+        <v>-1493195896</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -3028,7 +3014,7 @@
         <v>85</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>1768509650</v>
+        <v>1764132850</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -3049,7 +3035,7 @@
         <v>-44</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1372306928</v>
+        <v>-1368910672</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -3072,7 +3058,7 @@
         <v>51</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>2004768803</v>
+        <v>1999807297</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
@@ -3100,7 +3086,7 @@
         <v>25</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>433289914</v>
+        <v>432217586</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -3128,7 +3114,7 @@
         <v>8</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>124431975</v>
+        <v>124124025</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
@@ -3149,7 +3135,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억   ·   현금 2억(0.9%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 253억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
@@ -3245,11 +3231,11 @@
         <v>278</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>142336089</v>
+        <v>149452800</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>6.71%→7.29%</t>
+          <t>6.72%→7.30%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3266,11 +3252,11 @@
         <v>-67</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-112774470</v>
+        <v>-105484800</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>5.87%→5.39%</t>
+          <t>5.24%→4.80%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3289,11 +3275,11 @@
         <v>77</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>72688045</v>
+        <v>77320320</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>3.22%→3.51%</t>
+          <t>3.26%→3.56%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
@@ -3310,11 +3296,11 @@
         <v>-26</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>-71302445</v>
+        <v>-77708800</v>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2.97%→2.66%</t>
+          <t>3.08%→2.77%</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -3333,11 +3319,11 @@
         <v>31</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>59520037</v>
+        <v>64380800</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>6.64%→6.88%</t>
+          <t>6.85%→7.09%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -3354,11 +3340,11 @@
         <v>-24</v>
       </c>
       <c r="I80" s="15" t="n">
-        <v>-88627255</v>
+        <v>-97843200</v>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>4.94%→4.56%</t>
+          <t>5.20%→4.80%</t>
         </is>
       </c>
       <c r="K80" s="13" t="inlineStr">
@@ -3377,11 +3363,11 @@
         <v>10</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>39552025</v>
+        <v>42048000</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.21%</t>
+          <t>1.06%→1.22%</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
@@ -3398,11 +3384,11 @@
         <v>-15</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>-59808037</v>
+        <v>-50112000</v>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>1.51%→1.25%</t>
+          <t>1.20%→1.00%</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -3421,11 +3407,11 @@
         <v>7</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>49772831</v>
+        <v>53267200</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>2.30%→2.50%</t>
+          <t>2.34%→2.55%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
@@ -3442,11 +3428,11 @@
         <v>-8</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-55859235</v>
+        <v>-55910400</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.23%</t>
+          <t>1.40%→1.17%</t>
         </is>
       </c>
       <c r="K82" s="13" t="inlineStr">
@@ -3465,11 +3451,11 @@
         <v>6</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>36019223</v>
+        <v>38208000</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>1.81%→1.96%</t>
+          <t>1.83%→1.98%</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
@@ -3484,682 +3470,2131 @@
       <c r="K83" s="17" t="n"/>
     </row>
     <row r="85" ht="19" customHeight="1">
-      <c r="A85" s="18" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B85" s="19" t="n"/>
-      <c r="C85" s="19" t="n"/>
-      <c r="D85" s="19" t="n"/>
-      <c r="E85" s="19" t="n"/>
-      <c r="F85" s="19" t="n"/>
-      <c r="G85" s="19" t="n"/>
-      <c r="H85" s="19" t="n"/>
-      <c r="I85" s="19" t="n"/>
-      <c r="J85" s="19" t="n"/>
-      <c r="K85" s="19" t="n"/>
-    </row>
-    <row r="87" ht="19" customHeight="1">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B87" s="19" t="n"/>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="19" t="n"/>
-      <c r="E87" s="19" t="n"/>
-      <c r="F87" s="19" t="n"/>
-      <c r="G87" s="19" t="n"/>
-      <c r="H87" s="19" t="n"/>
-      <c r="I87" s="19" t="n"/>
-      <c r="J87" s="19" t="n"/>
-      <c r="K87" s="19" t="n"/>
-    </row>
-    <row r="89" ht="19" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억   ·   현금 2억(0.2%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 11종목  /  매도 12종목</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
-      <c r="J89" s="4" t="n"/>
-      <c r="K89" s="4" t="n"/>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 -2억(-0.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="8" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>475858967</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>2.64%→3.62%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>119→173</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (편출)</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>-179</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>-350983323</v>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.00%</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>179→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>삼성바이오로직스</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>1720488604</v>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>2.54%→6.69%</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>7→18</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>큐라클  (편출)</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>-99</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>-102702636</v>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>0.23%→0.00%</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>99→0</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="17" t="n"/>
+      <c r="B90" s="17" t="n"/>
+      <c r="C90" s="17" t="n"/>
+      <c r="D90" s="17" t="n"/>
+      <c r="E90" s="17" t="n"/>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I90" s="15" t="n">
+        <v>-399980540</v>
+      </c>
+      <c r="J90" s="16" t="inlineStr">
+        <is>
+          <t>5.42%→4.37%</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>297→244</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="n"/>
+      <c r="B91" s="17" t="n"/>
+      <c r="C91" s="17" t="n"/>
+      <c r="D91" s="17" t="n"/>
+      <c r="E91" s="17" t="n"/>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I91" s="15" t="n">
+        <v>-422438548</v>
+      </c>
+      <c r="J91" s="16" t="inlineStr">
+        <is>
+          <t>4.56%→3.01%</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>192→144</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="n"/>
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="17" t="n"/>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I92" s="15" t="n">
+        <v>-107616038</v>
+      </c>
+      <c r="J92" s="16" t="inlineStr">
+        <is>
+          <t>4.64%→4.84%</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>798→758</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="n"/>
+      <c r="B93" s="17" t="n"/>
+      <c r="C93" s="17" t="n"/>
+      <c r="D93" s="17" t="n"/>
+      <c r="E93" s="17" t="n"/>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <v>-182001064</v>
+      </c>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>5.46%→6.04%</t>
+        </is>
+      </c>
+      <c r="K93" s="13" t="inlineStr">
+        <is>
+          <t>464→433</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="n"/>
+      <c r="B94" s="17" t="n"/>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="17" t="n"/>
+      <c r="E94" s="17" t="n"/>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>휴젤  (편출)</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <v>-444805356</v>
+      </c>
+      <c r="J94" s="16" t="inlineStr">
+        <is>
+          <t>1.00%→0.00%</t>
+        </is>
+      </c>
+      <c r="K94" s="13" t="inlineStr">
+        <is>
+          <t>21→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="n"/>
+      <c r="B95" s="17" t="n"/>
+      <c r="C95" s="17" t="n"/>
+      <c r="D95" s="17" t="n"/>
+      <c r="E95" s="17" t="n"/>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I95" s="15" t="n">
+        <v>-312588110</v>
+      </c>
+      <c r="J95" s="16" t="inlineStr">
+        <is>
+          <t>3.65%→2.60%</t>
+        </is>
+      </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>54→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 70억(6.7%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 1종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="G90" s="7" t="inlineStr">
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="8" t="n"/>
-      <c r="J90" s="8" t="n"/>
-      <c r="K90" s="8" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="G99" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr">
+      <c r="H99" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K91" s="9" t="inlineStr">
+      <c r="K99" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>미코</t>
-        </is>
-      </c>
-      <c r="B92" s="11" t="n">
-        <v>333</v>
-      </c>
-      <c r="C92" s="11" t="n">
-        <v>1449216341</v>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>4.84%→7.35%</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t>1,206→1,539</t>
-        </is>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>엠케이전자</t>
-        </is>
-      </c>
-      <c r="H92" s="15" t="n">
-        <v>-501</v>
-      </c>
-      <c r="I92" s="15" t="n">
-        <v>-1240075492</v>
-      </c>
-      <c r="J92" s="16" t="inlineStr">
-        <is>
-          <t>3.02%→1.47%</t>
-        </is>
-      </c>
-      <c r="K92" s="13" t="inlineStr">
-        <is>
-          <t>1,041→540</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="n">
-        <v>288</v>
-      </c>
-      <c r="C93" s="11" t="n">
-        <v>872467405</v>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>5.23%→6.57%</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr">
-        <is>
-          <t>1,689→1,977</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H93" s="15" t="n">
-        <v>-387</v>
-      </c>
-      <c r="I93" s="15" t="n">
-        <v>-2457257078</v>
-      </c>
-      <c r="J93" s="16" t="inlineStr">
-        <is>
-          <t>3.72%→1.25%</t>
-        </is>
-      </c>
-      <c r="K93" s="13" t="inlineStr">
-        <is>
-          <t>566→179</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>아스플로</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="n">
-        <v>254</v>
-      </c>
-      <c r="C94" s="11" t="n">
-        <v>1368806322</v>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>2.29%→3.80%</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>389→643</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>디케이티</t>
-        </is>
-      </c>
-      <c r="H94" s="15" t="n">
-        <v>-189</v>
-      </c>
-      <c r="I94" s="15" t="n">
-        <v>-809676191</v>
-      </c>
-      <c r="J94" s="16" t="inlineStr">
-        <is>
-          <t>4.85%→4.54%</t>
-        </is>
-      </c>
-      <c r="K94" s="13" t="inlineStr">
-        <is>
-          <t>1,155→966</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>RFHIC  (신규)</t>
-        </is>
-      </c>
-      <c r="B95" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="C95" s="11" t="n">
-        <v>1829795431</v>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.01%</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="inlineStr">
-        <is>
-          <t>0→209</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>SFA  (편출)</t>
-        </is>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>-133</v>
-      </c>
-      <c r="I95" s="15" t="n">
-        <v>-614992145</v>
-      </c>
-      <c r="J95" s="16" t="inlineStr">
-        <is>
-          <t>0.69%→0.00%</t>
-        </is>
-      </c>
-      <c r="K95" s="13" t="inlineStr">
-        <is>
-          <t>133→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>에스티아이</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="n">
-        <v>168</v>
-      </c>
-      <c r="C96" s="11" t="n">
-        <v>815388192</v>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>2.03%→2.84%</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="inlineStr">
-        <is>
-          <t>365→533</t>
-        </is>
-      </c>
-      <c r="G96" s="14" t="inlineStr">
-        <is>
-          <t>태웅  (편출)</t>
-        </is>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>-95</v>
-      </c>
-      <c r="I96" s="15" t="n">
-        <v>-440087604</v>
-      </c>
-      <c r="J96" s="16" t="inlineStr">
-        <is>
-          <t>0.50%→0.00%</t>
-        </is>
-      </c>
-      <c r="K96" s="13" t="inlineStr">
-        <is>
-          <t>95→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>에프에스티</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="n">
-        <v>151</v>
-      </c>
-      <c r="C97" s="11" t="n">
-        <v>711059167</v>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>1.36%→2.11%</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="inlineStr">
-        <is>
-          <t>257→408</t>
-        </is>
-      </c>
-      <c r="G97" s="14" t="inlineStr">
-        <is>
-          <t>리노공업</t>
-        </is>
-      </c>
-      <c r="H97" s="15" t="n">
-        <v>-61</v>
-      </c>
-      <c r="I97" s="15" t="n">
-        <v>-658495155</v>
-      </c>
-      <c r="J97" s="16" t="inlineStr">
-        <is>
-          <t>4.58%→3.47%</t>
-        </is>
-      </c>
-      <c r="K97" s="13" t="inlineStr">
-        <is>
-          <t>354→293</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>동진쎄미켐</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="C98" s="11" t="n">
-        <v>459680108</v>
-      </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>3.00%→3.38%</t>
-        </is>
-      </c>
-      <c r="E98" s="13" t="inlineStr">
-        <is>
-          <t>371→436</t>
-        </is>
-      </c>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>티에스이</t>
-        </is>
-      </c>
-      <c r="H98" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I98" s="15" t="n">
-        <v>-1122000264</v>
-      </c>
-      <c r="J98" s="16" t="inlineStr">
-        <is>
-          <t>2.40%→1.13%</t>
-        </is>
-      </c>
-      <c r="K98" s="13" t="inlineStr">
-        <is>
-          <t>46→22</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>뉴파워프라즈마</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="C99" s="11" t="n">
-        <v>141372033</v>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>3.61%→4.10%</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr">
-        <is>
-          <t>1,373→1,427</t>
-        </is>
-      </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>프로텍</t>
-        </is>
-      </c>
-      <c r="H99" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I99" s="15" t="n">
-        <v>-267240063</v>
-      </c>
-      <c r="J99" s="16" t="inlineStr">
-        <is>
-          <t>0.71%→0.40%</t>
-        </is>
-      </c>
-      <c r="K99" s="13" t="inlineStr">
-        <is>
-          <t>57→33</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>321668861</v>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>3.74%→3.10%</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>25→28</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I100" s="15" t="n">
+        <v>-804692652</v>
+      </c>
+      <c r="J100" s="16" t="inlineStr">
+        <is>
+          <t>0.00%→1.16%</t>
+        </is>
+      </c>
+      <c r="K100" s="13" t="inlineStr">
+        <is>
+          <t>12→7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="n"/>
+      <c r="B101" s="17" t="n"/>
+      <c r="C101" s="17" t="n"/>
+      <c r="D101" s="17" t="n"/>
+      <c r="E101" s="17" t="n"/>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I101" s="15" t="n">
+        <v>-78199886</v>
+      </c>
+      <c r="J101" s="16" t="inlineStr">
+        <is>
+          <t>0.41%→0.22%</t>
+        </is>
+      </c>
+      <c r="K101" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="n"/>
+      <c r="B102" s="17" t="n"/>
+      <c r="C102" s="17" t="n"/>
+      <c r="D102" s="17" t="n"/>
+      <c r="E102" s="17" t="n"/>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I102" s="15" t="n">
+        <v>-551313362</v>
+      </c>
+      <c r="J102" s="16" t="inlineStr">
+        <is>
+          <t>7.68%→5.13%</t>
+        </is>
+      </c>
+      <c r="K102" s="13" t="inlineStr">
+        <is>
+          <t>40→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 913억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 11종목  /  매도 12종목</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>333</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>1449215489</v>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>4.84%→7.35%</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>1,206→1,539</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>엠케이전자</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>-501</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>-1240074762</v>
+      </c>
+      <c r="J107" s="16" t="inlineStr">
+        <is>
+          <t>3.02%→1.47%</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>1,041→540</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>288</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>872466892</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>5.23%→6.57%</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>1,689→1,977</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-387</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>-2457255633</v>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>3.72%→1.25%</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>566→179</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n">
+        <v>254</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>1368805517</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>2.29%→3.80%</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>389→643</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>디케이티</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-189</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>-809675714</v>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>4.85%→4.54%</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>1,155→966</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>RFHIC  (신규)</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
+        <v>209</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>1829794354</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.01%</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>0→209</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>SFA  (편출)</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>-614991783</v>
+      </c>
+      <c r="J110" s="16" t="inlineStr">
+        <is>
+          <t>0.69%→0.00%</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>133→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>에스티아이</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>815387712</v>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>2.03%→2.84%</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>365→533</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>태웅  (편출)</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>-440087345</v>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>0.50%→0.00%</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>95→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n">
+        <v>151</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>711058749</v>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>1.36%→2.11%</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>257→408</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>-61</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>-658494768</v>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t>4.58%→3.47%</t>
+        </is>
+      </c>
+      <c r="K112" s="13" t="inlineStr">
+        <is>
+          <t>354→293</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>동진쎄미켐</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>459679838</v>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>3.00%→3.38%</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>371→436</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>-1121999604</v>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t>2.40%→1.13%</t>
+        </is>
+      </c>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>46→22</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>141371950</v>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>3.61%→4.10%</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>1,373→1,427</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>-267239906</v>
+      </c>
+      <c r="J114" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.40%</t>
+        </is>
+      </c>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>57→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
           <t>인텍플러스</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n">
+      <c r="B115" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>552279130</v>
-      </c>
-      <c r="D100" s="12" t="inlineStr">
+      <c r="C115" s="11" t="n">
+        <v>552278805</v>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
         <is>
           <t>2.36%→3.17%</t>
         </is>
       </c>
-      <c r="E100" s="13" t="inlineStr">
+      <c r="E115" s="13" t="inlineStr">
         <is>
           <t>216→267</t>
         </is>
       </c>
-      <c r="G100" s="14" t="inlineStr">
+      <c r="G115" s="14" t="inlineStr">
         <is>
           <t>파크시스템스</t>
         </is>
       </c>
-      <c r="H100" s="15" t="n">
+      <c r="H115" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I100" s="15" t="n">
-        <v>-585225138</v>
-      </c>
-      <c r="J100" s="16" t="inlineStr">
+      <c r="I115" s="15" t="n">
+        <v>-585224793</v>
+      </c>
+      <c r="J115" s="16" t="inlineStr">
         <is>
           <t>1.93%→1.07%</t>
         </is>
       </c>
-      <c r="K100" s="13" t="inlineStr">
+      <c r="K115" s="13" t="inlineStr">
         <is>
           <t>40→25</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="B101" s="11" t="n">
+      <c r="B116" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>845342199</v>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
+      <c r="C116" s="11" t="n">
+        <v>845341702</v>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>1.01%→1.93%</t>
         </is>
       </c>
-      <c r="E101" s="13" t="inlineStr">
+      <c r="E116" s="13" t="inlineStr">
         <is>
           <t>50→96</t>
         </is>
       </c>
-      <c r="G101" s="14" t="inlineStr">
+      <c r="G116" s="14" t="inlineStr">
         <is>
           <t>티씨케이  (편출)</t>
         </is>
       </c>
-      <c r="H101" s="15" t="n">
+      <c r="H116" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I101" s="15" t="n">
-        <v>-510510120</v>
-      </c>
-      <c r="J101" s="16" t="inlineStr">
+      <c r="I116" s="15" t="n">
+        <v>-510509820</v>
+      </c>
+      <c r="J116" s="16" t="inlineStr">
         <is>
           <t>0.58%→0.00%</t>
         </is>
       </c>
-      <c r="K101" s="13" t="inlineStr">
+      <c r="K116" s="13" t="inlineStr">
         <is>
           <t>13→0</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>심텍</t>
         </is>
       </c>
-      <c r="B102" s="11" t="n">
+      <c r="B117" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>390150092</v>
-      </c>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="C117" s="11" t="n">
+        <v>390149862</v>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
         <is>
           <t>5.46%→5.80%</t>
         </is>
       </c>
-      <c r="E102" s="13" t="inlineStr">
+      <c r="E117" s="13" t="inlineStr">
         <is>
           <t>226→244</t>
         </is>
       </c>
-      <c r="G102" s="14" t="inlineStr">
+      <c r="G117" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H102" s="15" t="n">
+      <c r="H117" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I102" s="15" t="n">
-        <v>-164050039</v>
-      </c>
-      <c r="J102" s="16" t="inlineStr">
+      <c r="I117" s="15" t="n">
+        <v>-164049942</v>
+      </c>
+      <c r="J117" s="16" t="inlineStr">
         <is>
           <t>2.43%→2.30%</t>
         </is>
       </c>
-      <c r="K102" s="13" t="inlineStr">
+      <c r="K117" s="13" t="inlineStr">
         <is>
           <t>69→64</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="17" t="n"/>
-      <c r="B103" s="17" t="n"/>
-      <c r="C103" s="17" t="n"/>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="17" t="n"/>
-      <c r="G103" s="14" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="17" t="n"/>
+      <c r="B118" s="17" t="n"/>
+      <c r="C118" s="17" t="n"/>
+      <c r="D118" s="17" t="n"/>
+      <c r="E118" s="17" t="n"/>
+      <c r="G118" s="14" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="H103" s="15" t="n">
+      <c r="H118" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I103" s="15" t="n">
-        <v>-284580067</v>
-      </c>
-      <c r="J103" s="16" t="inlineStr">
+      <c r="I118" s="15" t="n">
+        <v>-284579900</v>
+      </c>
+      <c r="J118" s="16" t="inlineStr">
         <is>
           <t>4.04%→3.51%</t>
         </is>
       </c>
-      <c r="K103" s="13" t="inlineStr">
+      <c r="K118" s="13" t="inlineStr">
         <is>
           <t>49→45</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="19" t="n"/>
-      <c r="D105" s="19" t="n"/>
-      <c r="E105" s="19" t="n"/>
-      <c r="F105" s="19" t="n"/>
-      <c r="G105" s="19" t="n"/>
-      <c r="H105" s="19" t="n"/>
-      <c r="I105" s="19" t="n"/>
-      <c r="J105" s="19" t="n"/>
-      <c r="K105" s="19" t="n"/>
-    </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="18" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B107" s="19" t="n"/>
-      <c r="C107" s="19" t="n"/>
-      <c r="D107" s="19" t="n"/>
-      <c r="E107" s="19" t="n"/>
-      <c r="F107" s="19" t="n"/>
-      <c r="G107" s="19" t="n"/>
-      <c r="H107" s="19" t="n"/>
-      <c r="I107" s="19" t="n"/>
-      <c r="J107" s="19" t="n"/>
-      <c r="K107" s="19" t="n"/>
+    <row r="120" ht="19" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 0억(0.1%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 15종목  /  매도 14종목</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
+      <c r="K120" s="4" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="8" t="n"/>
+      <c r="J121" s="8" t="n"/>
+      <c r="K121" s="8" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>와이씨  (신규)</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>319185284</v>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.04%</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>0→54</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-139</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>-213301704</v>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>1.20%→0.49%</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>237→98</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>아이씨티케이  (신규)</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>331663721</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.08%</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>0→39</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-79</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>-256759419</v>
+      </c>
+      <c r="J124" s="16" t="inlineStr">
+        <is>
+          <t>2.89%→2.02%</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>270→191</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>루닛  (신규)</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>230211165</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.75%</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>0→38</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션  (편출)</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-250915940</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>0.83%→0.00%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>40→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>150629554</v>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.49%</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>0→37</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-26</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>-355197616</v>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>4.05%→2.84%</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>90→64</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>태웅  (신규)</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>300004529</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.97%</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>0→28</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>-110436694</v>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>3.64%→3.23%</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>240→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>294994630</v>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>2.30%→3.22%</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>26→37</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>-103212335</v>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
+        <is>
+          <t>2.21%→1.84%</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>117→99</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>216814948</v>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>1.36%→2.04%</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>19→29</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>-239338443</v>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
+        <is>
+          <t>1.52%→0.73%</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>29→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>319412624</v>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.04%</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>-416789901</v>
+      </c>
+      <c r="J130" s="16" t="inlineStr">
+        <is>
+          <t>2.93%→1.53%</t>
+        </is>
+      </c>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>32→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>375742411</v>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>6.01%→7.15%</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>34→41</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>-88830979</v>
+      </c>
+      <c r="J131" s="16" t="inlineStr">
+        <is>
+          <t>1.00%→0.69%</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>34→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>한양디지텍</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>103565975</v>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>4.66%→4.94%</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>-75443182</v>
+      </c>
+      <c r="J132" s="16" t="inlineStr">
+        <is>
+          <t>0.99%→0.74%</t>
+        </is>
+      </c>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>28→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>182040357</v>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>0.45%→1.04%</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>3→7</t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>-311708326</v>
+      </c>
+      <c r="J133" s="16" t="inlineStr">
+        <is>
+          <t>1.71%→0.68%</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>10→4</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>피엠티  (신규)</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>4268939</v>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.01%</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="inlineStr">
+        <is>
+          <t>0→3</t>
+        </is>
+      </c>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>태성</t>
+        </is>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I134" s="15" t="n">
+        <v>-136656568</v>
+      </c>
+      <c r="J134" s="16" t="inlineStr">
+        <is>
+          <t>1.95%→1.48%</t>
+        </is>
+      </c>
+      <c r="K134" s="13" t="inlineStr">
+        <is>
+          <t>26→20</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>43952390</v>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>0.82%→0.95%</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>17→20</t>
+        </is>
+      </c>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I135" s="15" t="n">
+        <v>-87988979</v>
+      </c>
+      <c r="J135" s="16" t="inlineStr">
+        <is>
+          <t>0.99%→0.69%</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>17→12</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>HT로보틱스  (신규)</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>11366997</v>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.04%</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>0→3</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I136" s="15" t="n">
+        <v>-122889871</v>
+      </c>
+      <c r="J136" s="16" t="inlineStr">
+        <is>
+          <t>3.37%→2.93%</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>25→22</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>18048266</v>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>0.22%→0.27%</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>11→14</t>
+        </is>
+      </c>
+      <c r="G137" s="17" t="n"/>
+      <c r="H137" s="17" t="n"/>
+      <c r="I137" s="17" t="n"/>
+      <c r="J137" s="17" t="n"/>
+      <c r="K137" s="17" t="n"/>
+    </row>
+    <row r="139" ht="19" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="n"/>
+      <c r="J139" s="4" t="n"/>
+      <c r="K139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="6" t="n"/>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="n"/>
+      <c r="I140" s="8" t="n"/>
+      <c r="J140" s="8" t="n"/>
+      <c r="K140" s="8" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K141" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>25301760</v>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.43%</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>-32026400</v>
+      </c>
+      <c r="J142" s="16" t="inlineStr">
+        <is>
+          <t>3.84%→3.28%</t>
+        </is>
+      </c>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>22848000</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>3.15%→3.54%</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I143" s="15" t="n">
+        <v>-26633600</v>
+      </c>
+      <c r="J143" s="16" t="inlineStr">
+        <is>
+          <t>4.53%→4.07%</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>9379200</v>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>2.38%→2.54%</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H144" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I144" s="15" t="n">
+        <v>-29336000</v>
+      </c>
+      <c r="J144" s="16" t="inlineStr">
+        <is>
+          <t>5.36%→4.85%</t>
+        </is>
+      </c>
+      <c r="K144" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>36828000</v>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>5.81%→6.44%</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G145" s="17" t="n"/>
+      <c r="H145" s="17" t="n"/>
+      <c r="I145" s="17" t="n"/>
+      <c r="J145" s="17" t="n"/>
+      <c r="K145" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A107:K107"/>
+  <mergeCells count="32">
+    <mergeCell ref="G105:K105"/>
+    <mergeCell ref="G86:K86"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="G98:K98"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A87:K87"/>
     <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A90:E90"/>
     <mergeCell ref="G66:K66"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
@@ -4167,17 +5602,24 @@
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A89:K89"/>
-    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="G121:K121"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A104:K104"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A85:K85"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A97:K97"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G76:K76"/>
-    <mergeCell ref="G90:K90"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="G140:K140"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -2403,23 +2403,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-820410246</v>
+        <v>-3518426055</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.88%</t>
+          <t>2.85%→1.26%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>300→250</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-3518426055</v>
+        <v>-820410246</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.85%→1.26%</t>
+          <t>1.97%→1.88%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>300→250</t>
         </is>
       </c>
     </row>
@@ -2667,23 +2667,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1629147988</v>
+        <v>-1103885331</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.58%→0.75%</t>
+          <t>1.22%→0.71%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2695,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1103885331</v>
+        <v>-1629147988</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.71%</t>
+          <t>1.58%→0.75%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 -2억(-0.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 8종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B85" s="4" t="n"/>
@@ -3817,7 +3817,7 @@
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 70억(6.7%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 1종목  /  매도 3종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
@@ -4380,23 +4380,23 @@
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>프로텍</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-1121999604</v>
+        <v>-267239906</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2.40%→1.13%</t>
+          <t>0.71%→0.40%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>46→22</t>
+          <t>57→33</t>
         </is>
       </c>
     </row>
@@ -4424,23 +4424,23 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-267239906</v>
+        <v>-1121999604</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.40%</t>
+          <t>2.40%→1.13%</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>57→33</t>
+          <t>46→22</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
     <row r="120" ht="19" customHeight="1">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 0억(0.1%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 15종목  /  매도 14종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 15종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
@@ -5157,41 +5157,41 @@
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-311708326</v>
+        <v>-136656568</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>1.71%→0.68%</t>
+          <t>1.95%→1.48%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>10→4</t>
+          <t>26→20</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>4268939</v>
+        <v>11366997</v>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
@@ -5201,46 +5201,46 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H134" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I134" s="15" t="n">
-        <v>-136656568</v>
+        <v>-311708326</v>
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>1.95%→1.48%</t>
+          <t>1.71%→0.68%</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>26→20</t>
+          <t>10→4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한라IMS</t>
         </is>
       </c>
       <c r="B135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>43952390</v>
+        <v>18048266</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.95%</t>
+          <t>0.22%→0.27%</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>11→14</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
@@ -5268,18 +5268,18 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>11366997</v>
+        <v>4268939</v>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
@@ -5312,23 +5312,23 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>한라IMS</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B137" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>18048266</v>
+        <v>43952390</v>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.27%</t>
+          <t>0.82%→0.95%</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>11→14</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G137" s="17" t="n"/>
@@ -5340,7 +5340,7 @@
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B139" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -2667,23 +2667,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1103885331</v>
+        <v>-1629147988</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.71%</t>
+          <t>1.58%→0.75%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2695,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1629147988</v>
+        <v>-1103885331</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.58%→0.75%</t>
+          <t>1.22%→0.71%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2751,23 +2751,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>파크시스템스  (편출)</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-5303652090</v>
+        <v>-3180923954</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>3.68%→1.41%</t>
+          <t>1.36%→0.00%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
@@ -2779,23 +2779,23 @@
       <c r="E62" s="17" t="n"/>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스  (편출)</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-3180923954</v>
+        <v>-5303652090</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.36%→0.00%</t>
+          <t>3.68%→1.41%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -3955,23 +3955,23 @@
       <c r="E101" s="17" t="n"/>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H101" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>-78199886</v>
+        <v>-551313362</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.22%</t>
+          <t>7.68%→5.13%</t>
         </is>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -3983,23 +3983,23 @@
       <c r="E102" s="17" t="n"/>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H102" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I102" s="15" t="n">
-        <v>-551313362</v>
+        <v>-78199886</v>
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>7.68%→5.13%</t>
+          <t>0.41%→0.22%</t>
         </is>
       </c>
       <c r="K102" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -4380,23 +4380,23 @@
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-267239906</v>
+        <v>-1121999604</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.40%</t>
+          <t>2.40%→1.13%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>57→33</t>
+          <t>46→22</t>
         </is>
       </c>
     </row>
@@ -4424,23 +4424,23 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>프로텍</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-1121999604</v>
+        <v>-267239906</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>2.40%→1.13%</t>
+          <t>0.71%→0.40%</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>46→22</t>
+          <t>57→33</t>
         </is>
       </c>
     </row>
@@ -4981,23 +4981,23 @@
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H129" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>-239338443</v>
+        <v>-416789901</v>
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.73%</t>
+          <t>2.93%→1.53%</t>
         </is>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -5025,23 +5025,23 @@
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H130" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I130" s="15" t="n">
-        <v>-416789901</v>
+        <v>-239338443</v>
       </c>
       <c r="J130" s="16" t="inlineStr">
         <is>
-          <t>2.93%→1.53%</t>
+          <t>1.52%→0.73%</t>
         </is>
       </c>
       <c r="K130" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -5157,41 +5157,41 @@
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-136656568</v>
+        <v>-311708326</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>1.95%→1.48%</t>
+          <t>1.71%→0.68%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>26→20</t>
+          <t>10→4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>11366997</v>
+        <v>4268939</v>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
@@ -5201,46 +5201,46 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H134" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I134" s="15" t="n">
-        <v>-311708326</v>
+        <v>-136656568</v>
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>1.71%→0.68%</t>
+          <t>1.95%→1.48%</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>10→4</t>
+          <t>26→20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>한라IMS</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>18048266</v>
+        <v>43952390</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.27%</t>
+          <t>0.82%→0.95%</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>11→14</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
@@ -5268,23 +5268,23 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>한라IMS</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>4268939</v>
+        <v>18048266</v>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.22%→0.27%</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>11→14</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
@@ -5312,23 +5312,23 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B137" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>43952390</v>
+        <v>11366997</v>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.95%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G137" s="17" t="n"/>

--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,17 @@
       <b val="1"/>
       <color rgb="000070C0"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +100,11 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -118,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -157,6 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -548,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-22 ~ 2026-10-29  (최근 5거래일)  ·  캡처 10/10</t>
+          <t>최근 5거래일 변화  ·  2026-10-22 ~ 2026-10-29  (최근 5거래일)  ·  캡처 15/19  ·  대기: RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -2403,23 +2422,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-3518426055</v>
+        <v>-820410246</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.85%→1.26%</t>
+          <t>1.97%→1.88%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>300→250</t>
         </is>
       </c>
     </row>
@@ -2447,23 +2466,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-820410246</v>
+        <v>-3518426055</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.88%</t>
+          <t>2.85%→1.26%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>300→250</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -2667,23 +2686,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1629147988</v>
+        <v>-1103885331</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.58%→0.75%</t>
+          <t>1.22%→0.71%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2714,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1103885331</v>
+        <v>-1629147988</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.71%</t>
+          <t>1.58%→0.75%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2751,23 +2770,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스  (편출)</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-3180923954</v>
+        <v>-5303652090</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.36%→0.00%</t>
+          <t>3.68%→1.41%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -2779,23 +2798,23 @@
       <c r="E62" s="17" t="n"/>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>파크시스템스  (편출)</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-5303652090</v>
+        <v>-3180923954</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>3.68%→1.41%</t>
+          <t>1.36%→0.00%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
@@ -4981,23 +5000,23 @@
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H129" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>-416789901</v>
+        <v>-239338443</v>
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2.93%→1.53%</t>
+          <t>1.52%→0.73%</t>
         </is>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -5025,23 +5044,23 @@
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H130" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I130" s="15" t="n">
-        <v>-239338443</v>
+        <v>-416789901</v>
       </c>
       <c r="J130" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.73%</t>
+          <t>2.93%→1.53%</t>
         </is>
       </c>
       <c r="K130" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -5157,90 +5176,90 @@
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-311708326</v>
+        <v>-136656568</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>1.71%→0.68%</t>
+          <t>1.95%→1.48%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>10→4</t>
+          <t>26→20</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>4268939</v>
+        <v>43952390</v>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.82%→0.95%</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H134" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I134" s="15" t="n">
-        <v>-136656568</v>
+        <v>-311708326</v>
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>1.95%→1.48%</t>
+          <t>1.71%→0.68%</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>26→20</t>
+          <t>10→4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>43952390</v>
+        <v>11366997</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.95%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
@@ -5268,23 +5287,23 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>한라IMS</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>18048266</v>
+        <v>4268939</v>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.27%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>11→14</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
@@ -5312,23 +5331,23 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>한라IMS</t>
         </is>
       </c>
       <c r="B137" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>11366997</v>
+        <v>18048266</v>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.22%→0.27%</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>11→14</t>
         </is>
       </c>
       <c r="G137" s="17" t="n"/>
@@ -5340,7 +5359,7 @@
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 4종목  /  매도 3종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 34억(1.0%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B139" s="4" t="n"/>
@@ -5429,172 +5448,1103 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>큐리언트  (신규)</t>
+          <t>네오셈  (신규)</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
-        <v>176</v>
+        <v>2567</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>25301760</v>
+        <v>7279447260</v>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.43%</t>
+          <t>0.00%→2.24%</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>0→176</t>
+          <t>0→2,567</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>HPSP  (편출)</t>
         </is>
       </c>
       <c r="H142" s="15" t="n">
-        <v>-98</v>
+        <v>-1305</v>
       </c>
       <c r="I142" s="15" t="n">
-        <v>-32026400</v>
+        <v>-10030099500</v>
       </c>
       <c r="J142" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.28%</t>
+          <t>3.32%→0.00%</t>
         </is>
       </c>
       <c r="K142" s="13" t="inlineStr">
         <is>
-          <t>683→585</t>
+          <t>1,305→0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>예스티  (신규)</t>
         </is>
       </c>
       <c r="B143" s="11" t="n">
-        <v>56</v>
+        <v>994</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>22848000</v>
+        <v>4232650800</v>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>3.15%→3.54%</t>
+          <t>0.00%→1.30%</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>449→505</t>
+          <t>0→994</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>네오티스</t>
         </is>
       </c>
       <c r="H143" s="15" t="n">
-        <v>-28</v>
+        <v>-423</v>
       </c>
       <c r="I143" s="15" t="n">
-        <v>-26633600</v>
+        <v>-1360494900</v>
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>4.53%→4.07%</t>
+          <t>3.39%→3.14%</t>
         </is>
       </c>
       <c r="K143" s="13" t="inlineStr">
         <is>
-          <t>277→249</t>
+          <t>3,595→3,172</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
-        <v>12</v>
+        <v>290</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>9379200</v>
+        <v>4414032000</v>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.54%</t>
+          <t>2.24%→3.68%</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>177→189</t>
+          <t>496→786</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이  (편출)</t>
         </is>
       </c>
       <c r="H144" s="15" t="n">
-        <v>-19</v>
+        <v>-231</v>
       </c>
       <c r="I144" s="15" t="n">
-        <v>-29336000</v>
+        <v>-4370589300</v>
       </c>
       <c r="J144" s="16" t="inlineStr">
         <is>
-          <t>5.36%→4.85%</t>
+          <t>1.45%→0.00%</t>
         </is>
       </c>
       <c r="K144" s="13" t="inlineStr">
         <is>
-          <t>202→183</t>
+          <t>231→0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
+          <t>파크시스템스  (신규)</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>5579374500</v>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.72%</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>0→161</t>
+        </is>
+      </c>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>테스  (편출)</t>
+        </is>
+      </c>
+      <c r="H145" s="15" t="n">
+        <v>-213</v>
+      </c>
+      <c r="I145" s="15" t="n">
+        <v>-3862776300</v>
+      </c>
+      <c r="J145" s="16" t="inlineStr">
+        <is>
+          <t>1.28%→0.00%</t>
+        </is>
+      </c>
+      <c r="K145" s="13" t="inlineStr">
+        <is>
+          <t>213→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>1697602400</v>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>4.02%→4.37%</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>766→870</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>-1024233000</v>
+      </c>
+      <c r="J146" s="16" t="inlineStr">
+        <is>
+          <t>2.32%→1.80%</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>895→762</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>591618000</v>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>4.38%→4.73%</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>75→78</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-83</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>-3032986000</v>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>25.22%→24.41%</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>2,256→2,173</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B149" s="19" t="n"/>
+      <c r="C149" s="19" t="n"/>
+      <c r="D149" s="19" t="n"/>
+      <c r="E149" s="19" t="n"/>
+      <c r="F149" s="19" t="n"/>
+      <c r="G149" s="19" t="n"/>
+      <c r="H149" s="19" t="n"/>
+      <c r="I149" s="19" t="n"/>
+      <c r="J149" s="19" t="n"/>
+      <c r="K149" s="19" t="n"/>
+    </row>
+    <row r="151" ht="19" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="n"/>
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="n"/>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="n"/>
+      <c r="J151" s="4" t="n"/>
+      <c r="K151" s="4" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="6" t="n"/>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="n"/>
+      <c r="I152" s="8" t="n"/>
+      <c r="J152" s="8" t="n"/>
+      <c r="K152" s="8" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C154" s="11" t="n">
+        <v>761484000</v>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>4.56%→5.14%</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G154" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I154" s="15" t="n">
+        <v>-832396500</v>
+      </c>
+      <c r="J154" s="16" t="inlineStr">
+        <is>
+          <t>3.02%→1.78%</t>
+        </is>
+      </c>
+      <c r="K154" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C155" s="11" t="n">
+        <v>890692000</v>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>2.90%→4.19%</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>63→85</t>
+        </is>
+      </c>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>삼성에스디에스</t>
+        </is>
+      </c>
+      <c r="H155" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I155" s="15" t="n">
+        <v>-807007500</v>
+      </c>
+      <c r="J155" s="16" t="inlineStr">
+        <is>
+          <t>1.79%→0.91%</t>
+        </is>
+      </c>
+      <c r="K155" s="13" t="inlineStr">
+        <is>
+          <t>225→108</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="19" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 5종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
+      <c r="E157" s="4" t="n"/>
+      <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="n"/>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="n"/>
+      <c r="J157" s="4" t="n"/>
+      <c r="K157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+      <c r="E158" s="6" t="n"/>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="n"/>
+      <c r="I158" s="8" t="n"/>
+      <c r="J158" s="8" t="n"/>
+      <c r="K158" s="8" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K159" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="n">
+        <v>314</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>988362304</v>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.84%</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>0→314</t>
+        </is>
+      </c>
+      <c r="G160" s="14" t="inlineStr">
+        <is>
+          <t>기가비스  (편출)</t>
+        </is>
+      </c>
+      <c r="H160" s="15" t="n">
+        <v>-275</v>
+      </c>
+      <c r="I160" s="15" t="n">
+        <v>-2883568095</v>
+      </c>
+      <c r="J160" s="16" t="inlineStr">
+        <is>
+          <t>5.28%→0.00%</t>
+        </is>
+      </c>
+      <c r="K160" s="13" t="inlineStr">
+        <is>
+          <t>275→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>디케이티  (신규)</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="C161" s="11" t="n">
+        <v>728431350</v>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.36%</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>0→298</t>
+        </is>
+      </c>
+      <c r="G161" s="14" t="inlineStr">
+        <is>
+          <t>HPSP  (편출)</t>
+        </is>
+      </c>
+      <c r="H161" s="15" t="n">
+        <v>-203</v>
+      </c>
+      <c r="I161" s="15" t="n">
+        <v>-931384492</v>
+      </c>
+      <c r="J161" s="16" t="inlineStr">
+        <is>
+          <t>1.71%→0.00%</t>
+        </is>
+      </c>
+      <c r="K161" s="13" t="inlineStr">
+        <is>
+          <t>203→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>코세스  (신규)</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="n">
+        <v>268</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>970950800</v>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.81%</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>0→268</t>
+        </is>
+      </c>
+      <c r="G162" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H162" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I162" s="15" t="n">
+        <v>-203903742</v>
+      </c>
+      <c r="J162" s="16" t="inlineStr">
+        <is>
+          <t>9.97%→9.78%</t>
+        </is>
+      </c>
+      <c r="K162" s="13" t="inlineStr">
+        <is>
+          <t>881→848</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>GST  (신규)</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="C163" s="11" t="n">
+        <v>681172940</v>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.27%</t>
+        </is>
+      </c>
+      <c r="E163" s="13" t="inlineStr">
+        <is>
+          <t>0→154</t>
+        </is>
+      </c>
+      <c r="G163" s="17" t="n"/>
+      <c r="H163" s="17" t="n"/>
+      <c r="I163" s="17" t="n"/>
+      <c r="J163" s="17" t="n"/>
+      <c r="K163" s="17" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C164" s="11" t="n">
+        <v>580351120</v>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>5.93%→7.13%</t>
+        </is>
+      </c>
+      <c r="E164" s="13" t="inlineStr">
+        <is>
+          <t>173→204</t>
+        </is>
+      </c>
+      <c r="G164" s="17" t="n"/>
+      <c r="H164" s="17" t="n"/>
+      <c r="I164" s="17" t="n"/>
+      <c r="J164" s="17" t="n"/>
+      <c r="K164" s="17" t="n"/>
+    </row>
+    <row r="166" ht="19" customHeight="1">
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="n"/>
+      <c r="C166" s="19" t="n"/>
+      <c r="D166" s="19" t="n"/>
+      <c r="E166" s="19" t="n"/>
+      <c r="F166" s="19" t="n"/>
+      <c r="G166" s="19" t="n"/>
+      <c r="H166" s="19" t="n"/>
+      <c r="I166" s="19" t="n"/>
+      <c r="J166" s="19" t="n"/>
+      <c r="K166" s="19" t="n"/>
+    </row>
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B168" s="19" t="n"/>
+      <c r="C168" s="19" t="n"/>
+      <c r="D168" s="19" t="n"/>
+      <c r="E168" s="19" t="n"/>
+      <c r="F168" s="19" t="n"/>
+      <c r="G168" s="19" t="n"/>
+      <c r="H168" s="19" t="n"/>
+      <c r="I168" s="19" t="n"/>
+      <c r="J168" s="19" t="n"/>
+      <c r="K168" s="19" t="n"/>
+    </row>
+    <row r="170" ht="19" customHeight="1">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B170" s="19" t="n"/>
+      <c r="C170" s="19" t="n"/>
+      <c r="D170" s="19" t="n"/>
+      <c r="E170" s="19" t="n"/>
+      <c r="F170" s="19" t="n"/>
+      <c r="G170" s="19" t="n"/>
+      <c r="H170" s="19" t="n"/>
+      <c r="I170" s="19" t="n"/>
+      <c r="J170" s="19" t="n"/>
+      <c r="K170" s="19" t="n"/>
+    </row>
+    <row r="172" ht="19" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 1억(0.5%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="4" t="n"/>
+      <c r="F172" s="4" t="n"/>
+      <c r="G172" s="4" t="n"/>
+      <c r="H172" s="4" t="n"/>
+      <c r="I172" s="4" t="n"/>
+      <c r="J172" s="4" t="n"/>
+      <c r="K172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="20" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="19" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="4" t="n"/>
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="n"/>
+      <c r="G175" s="4" t="n"/>
+      <c r="H175" s="4" t="n"/>
+      <c r="I175" s="4" t="n"/>
+      <c r="J175" s="4" t="n"/>
+      <c r="K175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="20" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="19" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="4" t="n"/>
+      <c r="F178" s="4" t="n"/>
+      <c r="G178" s="4" t="n"/>
+      <c r="H178" s="4" t="n"/>
+      <c r="I178" s="4" t="n"/>
+      <c r="J178" s="4" t="n"/>
+      <c r="K178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="n"/>
+      <c r="C179" s="6" t="n"/>
+      <c r="D179" s="6" t="n"/>
+      <c r="E179" s="6" t="n"/>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H179" s="8" t="n"/>
+      <c r="I179" s="8" t="n"/>
+      <c r="J179" s="8" t="n"/>
+      <c r="K179" s="8" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G180" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K180" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C181" s="11" t="n">
+        <v>25301760</v>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.43%</t>
+        </is>
+      </c>
+      <c r="E181" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G181" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H181" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I181" s="15" t="n">
+        <v>-32026400</v>
+      </c>
+      <c r="J181" s="16" t="inlineStr">
+        <is>
+          <t>3.84%→3.28%</t>
+        </is>
+      </c>
+      <c r="K181" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>22848000</v>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>3.15%→3.54%</t>
+        </is>
+      </c>
+      <c r="E182" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G182" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H182" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I182" s="15" t="n">
+        <v>-26633600</v>
+      </c>
+      <c r="J182" s="16" t="inlineStr">
+        <is>
+          <t>4.53%→4.07%</t>
+        </is>
+      </c>
+      <c r="K182" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C183" s="11" t="n">
+        <v>9379200</v>
+      </c>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>2.38%→2.54%</t>
+        </is>
+      </c>
+      <c r="E183" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G183" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H183" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I183" s="15" t="n">
+        <v>-29336000</v>
+      </c>
+      <c r="J183" s="16" t="inlineStr">
+        <is>
+          <t>5.36%→4.85%</t>
+        </is>
+      </c>
+      <c r="K183" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
+        <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="B145" s="11" t="n">
+      <c r="B184" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C145" s="11" t="n">
+      <c r="C184" s="11" t="n">
         <v>36828000</v>
       </c>
-      <c r="D145" s="12" t="inlineStr">
+      <c r="D184" s="12" t="inlineStr">
         <is>
           <t>5.81%→6.44%</t>
         </is>
       </c>
-      <c r="E145" s="13" t="inlineStr">
+      <c r="E184" s="13" t="inlineStr">
         <is>
           <t>101→112</t>
         </is>
       </c>
-      <c r="G145" s="17" t="n"/>
-      <c r="H145" s="17" t="n"/>
-      <c r="I145" s="17" t="n"/>
-      <c r="J145" s="17" t="n"/>
-      <c r="K145" s="17" t="n"/>
+      <c r="G184" s="17" t="n"/>
+      <c r="H184" s="17" t="n"/>
+      <c r="I184" s="17" t="n"/>
+      <c r="J184" s="17" t="n"/>
+      <c r="K184" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="49">
+    <mergeCell ref="A176:K176"/>
+    <mergeCell ref="G158:K158"/>
     <mergeCell ref="G105:K105"/>
+    <mergeCell ref="A157:K157"/>
+    <mergeCell ref="A166:K166"/>
     <mergeCell ref="G86:K86"/>
     <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A178:K178"/>
     <mergeCell ref="G98:K98"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G179:K179"/>
+    <mergeCell ref="A168:K168"/>
     <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A172:K172"/>
     <mergeCell ref="G66:K66"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
@@ -5603,23 +6553,32 @@
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A158:E158"/>
     <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A149:K149"/>
+    <mergeCell ref="G152:K152"/>
     <mergeCell ref="G121:K121"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A139:K139"/>
     <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A179:E179"/>
     <mergeCell ref="A104:K104"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A85:K85"/>
+    <mergeCell ref="A175:K175"/>
+    <mergeCell ref="A151:K151"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A97:K97"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G76:K76"/>
+    <mergeCell ref="A152:E152"/>
     <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A170:K170"/>
     <mergeCell ref="G140:K140"/>
+    <mergeCell ref="A173:K173"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -2422,23 +2422,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-820410246</v>
+        <v>-3518426055</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.88%</t>
+          <t>2.85%→1.26%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>300→250</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -2466,23 +2466,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-3518426055</v>
+        <v>-820410246</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.85%→1.26%</t>
+          <t>1.97%→1.88%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>300→250</t>
         </is>
       </c>
     </row>
@@ -2686,23 +2686,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1103885331</v>
+        <v>-1629147988</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.71%</t>
+          <t>1.58%→0.75%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2714,23 +2714,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1629147988</v>
+        <v>-1103885331</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.58%→0.75%</t>
+          <t>1.22%→0.71%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3974,23 +3974,23 @@
       <c r="E101" s="17" t="n"/>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H101" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>-551313362</v>
+        <v>-78199886</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>7.68%→5.13%</t>
+          <t>0.41%→0.22%</t>
         </is>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -4002,23 +4002,23 @@
       <c r="E102" s="17" t="n"/>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H102" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I102" s="15" t="n">
-        <v>-78199886</v>
+        <v>-551313362</v>
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.22%</t>
+          <t>7.68%→5.13%</t>
         </is>
       </c>
       <c r="K102" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -4399,23 +4399,23 @@
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>프로텍</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-1121999604</v>
+        <v>-267239906</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2.40%→1.13%</t>
+          <t>0.71%→0.40%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>46→22</t>
+          <t>57→33</t>
         </is>
       </c>
     </row>
@@ -4443,23 +4443,23 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-267239906</v>
+        <v>-1121999604</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.40%</t>
+          <t>2.40%→1.13%</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>57→33</t>
+          <t>46→22</t>
         </is>
       </c>
     </row>
@@ -5000,23 +5000,23 @@
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H129" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>-239338443</v>
+        <v>-416789901</v>
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.73%</t>
+          <t>2.93%→1.53%</t>
         </is>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -5044,23 +5044,23 @@
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H130" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I130" s="15" t="n">
-        <v>-416789901</v>
+        <v>-239338443</v>
       </c>
       <c r="J130" s="16" t="inlineStr">
         <is>
-          <t>2.93%→1.53%</t>
+          <t>1.52%→0.73%</t>
         </is>
       </c>
       <c r="K130" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -5176,85 +5176,85 @@
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-136656568</v>
+        <v>-311708326</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>1.95%→1.48%</t>
+          <t>1.71%→0.68%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>26→20</t>
+          <t>10→4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한라IMS</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>43952390</v>
+        <v>18048266</v>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.95%</t>
+          <t>0.22%→0.27%</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>11→14</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H134" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I134" s="15" t="n">
-        <v>-311708326</v>
+        <v>-136656568</v>
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>1.71%→0.68%</t>
+          <t>1.95%→1.48%</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>10→4</t>
+          <t>26→20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>11366997</v>
+        <v>4268939</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
@@ -5287,18 +5287,18 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>4268939</v>
+        <v>11366997</v>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
@@ -5331,23 +5331,23 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>한라IMS</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B137" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>18048266</v>
+        <v>43952390</v>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.27%</t>
+          <t>0.82%→0.95%</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>11→14</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G137" s="17" t="n"/>
@@ -5359,7 +5359,7 @@
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 34억(1.0%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 6종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B139" s="4" t="n"/>
@@ -5729,7 +5729,7 @@
     <row r="151" ht="19" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 2종목</t>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B151" s="4" t="n"/>
@@ -5906,7 +5906,7 @@
     <row r="157" ht="19" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 5종목  /  매도 3종목</t>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B157" s="4" t="n"/>
@@ -6234,7 +6234,7 @@
     <row r="172" ht="19" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 1억(0.5%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B172" s="4" t="n"/>
@@ -6258,7 +6258,7 @@
     <row r="175" ht="19" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B175" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K184"/>
+  <dimension ref="A1:K213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-22 ~ 2026-10-29  (최근 5거래일)  ·  캡처 15/19  ·  대기: RISE, RISE, DS, RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-22 ~ 2026-10-29  (최근 5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -2290,23 +2290,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-66</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-2005202701</v>
+        <v>-5234217369</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.49%→0.68%</t>
+          <t>3.09%→0.87%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>115→49</t>
+          <t>90→24</t>
         </is>
       </c>
     </row>
@@ -2334,23 +2334,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-66</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-5234217369</v>
+        <v>-2005202701</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>3.09%→0.87%</t>
+          <t>1.49%→0.68%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>90→24</t>
+          <t>115→49</t>
         </is>
       </c>
     </row>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-3518426055</v>
+        <v>-820410246</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.85%→1.26%</t>
+          <t>1.97%→1.88%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>300→250</t>
         </is>
       </c>
     </row>
@@ -2466,23 +2466,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-820410246</v>
+        <v>-3518426055</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.88%</t>
+          <t>2.85%→1.26%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>300→250</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -4399,23 +4399,23 @@
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-267239906</v>
+        <v>-1121999604</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.40%</t>
+          <t>2.40%→1.13%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>57→33</t>
+          <t>46→22</t>
         </is>
       </c>
     </row>
@@ -4443,23 +4443,23 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>프로텍</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-1121999604</v>
+        <v>-267239906</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>2.40%→1.13%</t>
+          <t>0.71%→0.40%</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>46→22</t>
+          <t>57→33</t>
         </is>
       </c>
     </row>
@@ -5243,23 +5243,23 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>4268939</v>
+        <v>43952390</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.82%→0.95%</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
@@ -5331,23 +5331,23 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B137" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>43952390</v>
+        <v>4268939</v>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.95%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G137" s="17" t="n"/>
@@ -5359,7 +5359,7 @@
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 6종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 21억(0.5%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B139" s="4" t="n"/>
@@ -5374,1211 +5374,2041 @@
       <c r="K139" s="4" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="19" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 6종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="n"/>
+      <c r="J142" s="4" t="n"/>
+      <c r="K142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="G140" s="7" t="inlineStr">
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+      <c r="E143" s="6" t="n"/>
+      <c r="G143" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H140" s="8" t="n"/>
-      <c r="I140" s="8" t="n"/>
-      <c r="J140" s="8" t="n"/>
-      <c r="K140" s="8" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="H143" s="8" t="n"/>
+      <c r="I143" s="8" t="n"/>
+      <c r="J143" s="8" t="n"/>
+      <c r="K143" s="8" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D141" s="9" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E141" s="9" t="inlineStr">
+      <c r="E144" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G141" s="9" t="inlineStr">
+      <c r="G144" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H141" s="9" t="inlineStr">
+      <c r="H144" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I141" s="9" t="inlineStr">
+      <c r="I144" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J141" s="9" t="inlineStr">
+      <c r="J144" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K141" s="9" t="inlineStr">
+      <c r="K144" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="10" t="inlineStr">
-        <is>
-          <t>네오셈  (신규)</t>
-        </is>
-      </c>
-      <c r="B142" s="11" t="n">
-        <v>2567</v>
-      </c>
-      <c r="C142" s="11" t="n">
-        <v>7279447260</v>
-      </c>
-      <c r="D142" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.24%</t>
-        </is>
-      </c>
-      <c r="E142" s="13" t="inlineStr">
-        <is>
-          <t>0→2,567</t>
-        </is>
-      </c>
-      <c r="G142" s="14" t="inlineStr">
-        <is>
-          <t>HPSP  (편출)</t>
-        </is>
-      </c>
-      <c r="H142" s="15" t="n">
-        <v>-1305</v>
-      </c>
-      <c r="I142" s="15" t="n">
-        <v>-10030099500</v>
-      </c>
-      <c r="J142" s="16" t="inlineStr">
-        <is>
-          <t>3.32%→0.00%</t>
-        </is>
-      </c>
-      <c r="K142" s="13" t="inlineStr">
-        <is>
-          <t>1,305→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="10" t="inlineStr">
-        <is>
-          <t>예스티  (신규)</t>
-        </is>
-      </c>
-      <c r="B143" s="11" t="n">
-        <v>994</v>
-      </c>
-      <c r="C143" s="11" t="n">
-        <v>4232650800</v>
-      </c>
-      <c r="D143" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.30%</t>
-        </is>
-      </c>
-      <c r="E143" s="13" t="inlineStr">
-        <is>
-          <t>0→994</t>
-        </is>
-      </c>
-      <c r="G143" s="14" t="inlineStr">
-        <is>
-          <t>네오티스</t>
-        </is>
-      </c>
-      <c r="H143" s="15" t="n">
-        <v>-423</v>
-      </c>
-      <c r="I143" s="15" t="n">
-        <v>-1360494900</v>
-      </c>
-      <c r="J143" s="16" t="inlineStr">
-        <is>
-          <t>3.39%→3.14%</t>
-        </is>
-      </c>
-      <c r="K143" s="13" t="inlineStr">
-        <is>
-          <t>3,595→3,172</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>타이거일렉</t>
-        </is>
-      </c>
-      <c r="B144" s="11" t="n">
-        <v>290</v>
-      </c>
-      <c r="C144" s="11" t="n">
-        <v>4414032000</v>
-      </c>
-      <c r="D144" s="12" t="inlineStr">
-        <is>
-          <t>2.24%→3.68%</t>
-        </is>
-      </c>
-      <c r="E144" s="13" t="inlineStr">
-        <is>
-          <t>496→786</t>
-        </is>
-      </c>
-      <c r="G144" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이  (편출)</t>
-        </is>
-      </c>
-      <c r="H144" s="15" t="n">
-        <v>-231</v>
-      </c>
-      <c r="I144" s="15" t="n">
-        <v>-4370589300</v>
-      </c>
-      <c r="J144" s="16" t="inlineStr">
-        <is>
-          <t>1.45%→0.00%</t>
-        </is>
-      </c>
-      <c r="K144" s="13" t="inlineStr">
-        <is>
-          <t>231→0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스  (신규)</t>
+          <t>네오셈  (신규)</t>
         </is>
       </c>
       <c r="B145" s="11" t="n">
-        <v>161</v>
+        <v>2567</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>5579374500</v>
+        <v>7279447260</v>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.72%</t>
+          <t>0.00%→2.24%</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>0→161</t>
+          <t>0→2,567</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
-          <t>테스  (편출)</t>
+          <t>HPSP  (편출)</t>
         </is>
       </c>
       <c r="H145" s="15" t="n">
-        <v>-213</v>
+        <v>-1305</v>
       </c>
       <c r="I145" s="15" t="n">
-        <v>-3862776300</v>
+        <v>-10030099500</v>
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>1.28%→0.00%</t>
+          <t>3.32%→0.00%</t>
         </is>
       </c>
       <c r="K145" s="13" t="inlineStr">
         <is>
-          <t>213→0</t>
+          <t>1,305→0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>예스티  (신규)</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
-        <v>104</v>
+        <v>994</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1697602400</v>
+        <v>4232650800</v>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>4.02%→4.37%</t>
+          <t>0.00%→1.30%</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>766→870</t>
+          <t>0→994</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>네오티스</t>
         </is>
       </c>
       <c r="H146" s="15" t="n">
-        <v>-133</v>
+        <v>-423</v>
       </c>
       <c r="I146" s="15" t="n">
-        <v>-1024233000</v>
+        <v>-1360494900</v>
       </c>
       <c r="J146" s="16" t="inlineStr">
         <is>
-          <t>2.32%→1.80%</t>
+          <t>3.39%→3.14%</t>
         </is>
       </c>
       <c r="K146" s="13" t="inlineStr">
         <is>
-          <t>895→762</t>
+          <t>3,595→3,172</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="n">
+        <v>290</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>4414032000</v>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>2.24%→3.68%</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>496→786</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이  (편출)</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-231</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>-4370589300</v>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>1.45%→0.00%</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>231→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>파크시스템스  (신규)</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>5579374500</v>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.72%</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>0→161</t>
+        </is>
+      </c>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>테스  (편출)</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>-213</v>
+      </c>
+      <c r="I148" s="15" t="n">
+        <v>-3862776300</v>
+      </c>
+      <c r="J148" s="16" t="inlineStr">
+        <is>
+          <t>1.28%→0.00%</t>
+        </is>
+      </c>
+      <c r="K148" s="13" t="inlineStr">
+        <is>
+          <t>213→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="C149" s="11" t="n">
+        <v>1697602400</v>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>4.02%→4.37%</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>766→870</t>
+        </is>
+      </c>
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I149" s="15" t="n">
+        <v>-1024233000</v>
+      </c>
+      <c r="J149" s="16" t="inlineStr">
+        <is>
+          <t>2.32%→1.80%</t>
+        </is>
+      </c>
+      <c r="K149" s="13" t="inlineStr">
+        <is>
+          <t>895→762</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="B147" s="11" t="n">
+      <c r="B150" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C147" s="11" t="n">
+      <c r="C150" s="11" t="n">
         <v>591618000</v>
       </c>
-      <c r="D147" s="12" t="inlineStr">
+      <c r="D150" s="12" t="inlineStr">
         <is>
           <t>4.38%→4.73%</t>
         </is>
       </c>
-      <c r="E147" s="13" t="inlineStr">
+      <c r="E150" s="13" t="inlineStr">
         <is>
           <t>75→78</t>
         </is>
       </c>
-      <c r="G147" s="14" t="inlineStr">
+      <c r="G150" s="14" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="H147" s="15" t="n">
+      <c r="H150" s="15" t="n">
         <v>-83</v>
       </c>
-      <c r="I147" s="15" t="n">
+      <c r="I150" s="15" t="n">
         <v>-3032986000</v>
       </c>
-      <c r="J147" s="16" t="inlineStr">
+      <c r="J150" s="16" t="inlineStr">
         <is>
           <t>25.22%→24.41%</t>
         </is>
       </c>
-      <c r="K147" s="13" t="inlineStr">
+      <c r="K150" s="13" t="inlineStr">
         <is>
           <t>2,256→2,173</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="19" customHeight="1">
-      <c r="A149" s="18" t="inlineStr">
+    <row r="152" ht="19" customHeight="1">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="n"/>
+      <c r="C152" s="20" t="n"/>
+      <c r="D152" s="20" t="n"/>
+      <c r="E152" s="20" t="n"/>
+      <c r="F152" s="20" t="n"/>
+      <c r="G152" s="20" t="n"/>
+      <c r="H152" s="20" t="n"/>
+      <c r="I152" s="20" t="n"/>
+      <c r="J152" s="20" t="n"/>
+      <c r="K152" s="20" t="n"/>
+    </row>
+    <row r="154" ht="19" customHeight="1">
+      <c r="A154" s="19" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B149" s="19" t="n"/>
-      <c r="C149" s="19" t="n"/>
-      <c r="D149" s="19" t="n"/>
-      <c r="E149" s="19" t="n"/>
-      <c r="F149" s="19" t="n"/>
-      <c r="G149" s="19" t="n"/>
-      <c r="H149" s="19" t="n"/>
-      <c r="I149" s="19" t="n"/>
-      <c r="J149" s="19" t="n"/>
-      <c r="K149" s="19" t="n"/>
-    </row>
-    <row r="151" ht="19" customHeight="1">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="B154" s="20" t="n"/>
+      <c r="C154" s="20" t="n"/>
+      <c r="D154" s="20" t="n"/>
+      <c r="E154" s="20" t="n"/>
+      <c r="F154" s="20" t="n"/>
+      <c r="G154" s="20" t="n"/>
+      <c r="H154" s="20" t="n"/>
+      <c r="I154" s="20" t="n"/>
+      <c r="J154" s="20" t="n"/>
+      <c r="K154" s="20" t="n"/>
+    </row>
+    <row r="156" ht="19" customHeight="1">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B151" s="4" t="n"/>
-      <c r="C151" s="4" t="n"/>
-      <c r="D151" s="4" t="n"/>
-      <c r="E151" s="4" t="n"/>
-      <c r="F151" s="4" t="n"/>
-      <c r="G151" s="4" t="n"/>
-      <c r="H151" s="4" t="n"/>
-      <c r="I151" s="4" t="n"/>
-      <c r="J151" s="4" t="n"/>
-      <c r="K151" s="4" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="4" t="n"/>
+      <c r="D156" s="4" t="n"/>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="n"/>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="4" t="n"/>
+      <c r="J156" s="4" t="n"/>
+      <c r="K156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B152" s="6" t="n"/>
-      <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="n"/>
-      <c r="E152" s="6" t="n"/>
-      <c r="G152" s="7" t="inlineStr">
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="G157" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H152" s="8" t="n"/>
-      <c r="I152" s="8" t="n"/>
-      <c r="J152" s="8" t="n"/>
-      <c r="K152" s="8" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="H157" s="8" t="n"/>
+      <c r="I157" s="8" t="n"/>
+      <c r="J157" s="8" t="n"/>
+      <c r="K157" s="8" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B153" s="9" t="inlineStr">
+      <c r="B158" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C153" s="9" t="inlineStr">
+      <c r="C158" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D153" s="9" t="inlineStr">
+      <c r="D158" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E153" s="9" t="inlineStr">
+      <c r="E158" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G153" s="9" t="inlineStr">
+      <c r="G158" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H153" s="9" t="inlineStr">
+      <c r="H158" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I153" s="9" t="inlineStr">
+      <c r="I158" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J153" s="9" t="inlineStr">
+      <c r="J158" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K153" s="9" t="inlineStr">
+      <c r="K158" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="10" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
         <is>
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="B154" s="11" t="n">
+      <c r="B159" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C154" s="11" t="n">
+      <c r="C159" s="11" t="n">
         <v>761484000</v>
       </c>
-      <c r="D154" s="12" t="inlineStr">
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>4.56%→5.14%</t>
         </is>
       </c>
-      <c r="E154" s="13" t="inlineStr">
+      <c r="E159" s="13" t="inlineStr">
         <is>
           <t>209→255</t>
         </is>
       </c>
-      <c r="G154" s="14" t="inlineStr">
+      <c r="G159" s="14" t="inlineStr">
         <is>
           <t>대한전선</t>
         </is>
       </c>
-      <c r="H154" s="15" t="n">
+      <c r="H159" s="15" t="n">
         <v>-1215</v>
       </c>
-      <c r="I154" s="15" t="n">
+      <c r="I159" s="15" t="n">
         <v>-832396500</v>
       </c>
-      <c r="J154" s="16" t="inlineStr">
+      <c r="J159" s="16" t="inlineStr">
         <is>
           <t>3.02%→1.78%</t>
         </is>
       </c>
-      <c r="K154" s="13" t="inlineStr">
+      <c r="K159" s="13" t="inlineStr">
         <is>
           <t>3,349→2,134</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B155" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C155" s="11" t="n">
-        <v>890692000</v>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>2.90%→4.19%</t>
-        </is>
-      </c>
-      <c r="E155" s="13" t="inlineStr">
-        <is>
-          <t>63→85</t>
-        </is>
-      </c>
-      <c r="G155" s="14" t="inlineStr">
-        <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="H155" s="15" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I155" s="15" t="n">
-        <v>-807007500</v>
-      </c>
-      <c r="J155" s="16" t="inlineStr">
-        <is>
-          <t>1.79%→0.91%</t>
-        </is>
-      </c>
-      <c r="K155" s="13" t="inlineStr">
-        <is>
-          <t>225→108</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="19" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 5종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="n"/>
-      <c r="C157" s="4" t="n"/>
-      <c r="D157" s="4" t="n"/>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="4" t="n"/>
-      <c r="G157" s="4" t="n"/>
-      <c r="H157" s="4" t="n"/>
-      <c r="I157" s="4" t="n"/>
-      <c r="J157" s="4" t="n"/>
-      <c r="K157" s="4" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="n"/>
-      <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6" t="n"/>
-      <c r="E158" s="6" t="n"/>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H158" s="8" t="n"/>
-      <c r="I158" s="8" t="n"/>
-      <c r="J158" s="8" t="n"/>
-      <c r="K158" s="8" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B159" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E159" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G159" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H159" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I159" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J159" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K159" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>890692000</v>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>2.90%→4.19%</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>63→85</t>
+        </is>
+      </c>
+      <c r="G160" s="14" t="inlineStr">
+        <is>
+          <t>삼성에스디에스</t>
+        </is>
+      </c>
+      <c r="H160" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I160" s="15" t="n">
+        <v>-807007500</v>
+      </c>
+      <c r="J160" s="16" t="inlineStr">
+        <is>
+          <t>1.79%→0.91%</t>
+        </is>
+      </c>
+      <c r="K160" s="13" t="inlineStr">
+        <is>
+          <t>225→108</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="19" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 5억(1.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 12종목  /  매도 17종목</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="n"/>
+      <c r="C162" s="4" t="n"/>
+      <c r="D162" s="4" t="n"/>
+      <c r="E162" s="4" t="n"/>
+      <c r="F162" s="4" t="n"/>
+      <c r="G162" s="4" t="n"/>
+      <c r="H162" s="4" t="n"/>
+      <c r="I162" s="4" t="n"/>
+      <c r="J162" s="4" t="n"/>
+      <c r="K162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="n"/>
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="6" t="n"/>
+      <c r="E163" s="6" t="n"/>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="n"/>
+      <c r="I163" s="8" t="n"/>
+      <c r="J163" s="8" t="n"/>
+      <c r="K163" s="8" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K164" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈  (신규)</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="n">
+        <v>2522</v>
+      </c>
+      <c r="C165" s="11" t="n">
+        <v>874226080</v>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.37%</t>
+        </is>
+      </c>
+      <c r="E165" s="13" t="inlineStr">
+        <is>
+          <t>0→2,522</t>
+        </is>
+      </c>
+      <c r="G165" s="14" t="inlineStr">
+        <is>
+          <t>솔루엠  (편출)</t>
+        </is>
+      </c>
+      <c r="H165" s="15" t="n">
+        <v>-1922</v>
+      </c>
+      <c r="I165" s="15" t="n">
+        <v>-831457200</v>
+      </c>
+      <c r="J165" s="16" t="inlineStr">
+        <is>
+          <t>2.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K165" s="13" t="inlineStr">
+        <is>
+          <t>1,922→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="n">
+        <v>1566</v>
+      </c>
+      <c r="C166" s="11" t="n">
+        <v>424010160</v>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.15%</t>
+        </is>
+      </c>
+      <c r="E166" s="13" t="inlineStr">
+        <is>
+          <t>0→1,566</t>
+        </is>
+      </c>
+      <c r="G166" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H166" s="15" t="n">
+        <v>-541</v>
+      </c>
+      <c r="I166" s="15" t="n">
+        <v>-716500400</v>
+      </c>
+      <c r="J166" s="16" t="inlineStr">
+        <is>
+          <t>3.39%→1.15%</t>
+        </is>
+      </c>
+      <c r="K166" s="13" t="inlineStr">
+        <is>
+          <t>861→320</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C167" s="11" t="n">
+        <v>585779040</v>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.59%</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="inlineStr">
+        <is>
+          <t>0→1,174</t>
+        </is>
+      </c>
+      <c r="G167" s="14" t="inlineStr">
+        <is>
+          <t>에스티아이</t>
+        </is>
+      </c>
+      <c r="H167" s="15" t="n">
+        <v>-492</v>
+      </c>
+      <c r="I167" s="15" t="n">
+        <v>-393304800</v>
+      </c>
+      <c r="J167" s="16" t="inlineStr">
+        <is>
+          <t>2.98%→1.81%</t>
+        </is>
+      </c>
+      <c r="K167" s="13" t="inlineStr">
+        <is>
+          <t>1,328→836</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스  (신규)</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="n">
+        <v>324</v>
+      </c>
+      <c r="C168" s="11" t="n">
+        <v>577886400</v>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.56%</t>
+        </is>
+      </c>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>0→324</t>
+        </is>
+      </c>
+      <c r="G168" s="14" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀  (편출)</t>
+        </is>
+      </c>
+      <c r="H168" s="15" t="n">
+        <v>-321</v>
+      </c>
+      <c r="I168" s="15" t="n">
+        <v>-304243800</v>
+      </c>
+      <c r="J168" s="16" t="inlineStr">
+        <is>
+          <t>0.84%→0.00%</t>
+        </is>
+      </c>
+      <c r="K168" s="13" t="inlineStr">
+        <is>
+          <t>321→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>LG씨엔에스</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="n">
+        <v>306</v>
+      </c>
+      <c r="C169" s="11" t="n">
+        <v>676872000</v>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>2.77%→4.79%</t>
+        </is>
+      </c>
+      <c r="E169" s="13" t="inlineStr">
+        <is>
+          <t>494→800</t>
+        </is>
+      </c>
+      <c r="G169" s="14" t="inlineStr">
+        <is>
+          <t>비에이치아이  (편출)</t>
+        </is>
+      </c>
+      <c r="H169" s="15" t="n">
+        <v>-293</v>
+      </c>
+      <c r="I169" s="15" t="n">
+        <v>-390510400</v>
+      </c>
+      <c r="J169" s="16" t="inlineStr">
+        <is>
+          <t>1.08%→0.00%</t>
+        </is>
+      </c>
+      <c r="K169" s="13" t="inlineStr">
+        <is>
+          <t>293→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>ISC  (신규)</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="n">
+        <v>165</v>
+      </c>
+      <c r="C170" s="11" t="n">
+        <v>766458000</v>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.08%</t>
+        </is>
+      </c>
+      <c r="E170" s="13" t="inlineStr">
+        <is>
+          <t>0→165</t>
+        </is>
+      </c>
+      <c r="G170" s="14" t="inlineStr">
+        <is>
+          <t>DB하이텍  (편출)</t>
+        </is>
+      </c>
+      <c r="H170" s="15" t="n">
+        <v>-269</v>
+      </c>
+      <c r="I170" s="15" t="n">
+        <v>-781821600</v>
+      </c>
+      <c r="J170" s="16" t="inlineStr">
+        <is>
+          <t>2.16%→0.00%</t>
+        </is>
+      </c>
+      <c r="K170" s="13" t="inlineStr">
+        <is>
+          <t>269→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>345982000</v>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>5.12%→6.47%</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>384→449</t>
+        </is>
+      </c>
+      <c r="G171" s="14" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="H171" s="15" t="n">
+        <v>-212</v>
+      </c>
+      <c r="I171" s="15" t="n">
+        <v>-364470400</v>
+      </c>
+      <c r="J171" s="16" t="inlineStr">
+        <is>
+          <t>2.89%→1.75%</t>
+        </is>
+      </c>
+      <c r="K171" s="13" t="inlineStr">
+        <is>
+          <t>588→376</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="inlineStr">
+        <is>
+          <t>코리아써키트</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="C172" s="11" t="n">
+        <v>121413600</v>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>2.19%→2.72%</t>
+        </is>
+      </c>
+      <c r="E172" s="13" t="inlineStr">
+        <is>
+          <t>392→446</t>
+        </is>
+      </c>
+      <c r="G172" s="14" t="inlineStr">
+        <is>
+          <t>RFHIC</t>
+        </is>
+      </c>
+      <c r="H172" s="15" t="n">
+        <v>-191</v>
+      </c>
+      <c r="I172" s="15" t="n">
+        <v>-275422000</v>
+      </c>
+      <c r="J172" s="16" t="inlineStr">
+        <is>
+          <t>1.48%→0.82%</t>
+        </is>
+      </c>
+      <c r="K172" s="13" t="inlineStr">
+        <is>
+          <t>401→210</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="inlineStr">
+        <is>
+          <t>케이씨텍</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C173" s="11" t="n">
+        <v>88242000</v>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>4.99%→4.90%</t>
+        </is>
+      </c>
+      <c r="E173" s="13" t="inlineStr">
+        <is>
+          <t>644→677</t>
+        </is>
+      </c>
+      <c r="G173" s="14" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="H173" s="15" t="n">
+        <v>-136</v>
+      </c>
+      <c r="I173" s="15" t="n">
+        <v>-363664000</v>
+      </c>
+      <c r="J173" s="16" t="inlineStr">
+        <is>
+          <t>1.55%→0.58%</t>
+        </is>
+      </c>
+      <c r="K173" s="13" t="inlineStr">
+        <is>
+          <t>216→80</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>999264000</v>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>5.91%→9.36%</t>
+        </is>
+      </c>
+      <c r="E174" s="13" t="inlineStr">
+        <is>
+          <t>59→83</t>
+        </is>
+      </c>
+      <c r="G174" s="14" t="inlineStr">
+        <is>
+          <t>SK텔레콤  (편출)</t>
+        </is>
+      </c>
+      <c r="H174" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I174" s="15" t="n">
+        <v>-166658800</v>
+      </c>
+      <c r="J174" s="16" t="inlineStr">
+        <is>
+          <t>0.46%→0.00%</t>
+        </is>
+      </c>
+      <c r="K174" s="13" t="inlineStr">
+        <is>
+          <t>77→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C175" s="11" t="n">
+        <v>97272000</v>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
+        <is>
+          <t>5.57%→5.99%</t>
+        </is>
+      </c>
+      <c r="E175" s="13" t="inlineStr">
+        <is>
+          <t>391→409</t>
+        </is>
+      </c>
+      <c r="G175" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H175" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I175" s="15" t="n">
+        <v>-148573600</v>
+      </c>
+      <c r="J175" s="16" t="inlineStr">
+        <is>
+          <t>3.09%→2.57%</t>
+        </is>
+      </c>
+      <c r="K175" s="13" t="inlineStr">
+        <is>
+          <t>318→275</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>292544000</v>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>0.63%→1.49%</t>
+        </is>
+      </c>
+      <c r="E176" s="13" t="inlineStr">
+        <is>
+          <t>7→15</t>
+        </is>
+      </c>
+      <c r="G176" s="14" t="inlineStr">
+        <is>
+          <t>LS ELECTRIC</t>
+        </is>
+      </c>
+      <c r="H176" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I176" s="15" t="n">
+        <v>-106002400</v>
+      </c>
+      <c r="J176" s="16" t="inlineStr">
+        <is>
+          <t>3.65%→3.26%</t>
+        </is>
+      </c>
+      <c r="K176" s="13" t="inlineStr">
+        <is>
+          <t>284→261</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="17" t="n"/>
+      <c r="B177" s="17" t="n"/>
+      <c r="C177" s="17" t="n"/>
+      <c r="D177" s="17" t="n"/>
+      <c r="E177" s="17" t="n"/>
+      <c r="G177" s="14" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="H177" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I177" s="15" t="n">
+        <v>-343896000</v>
+      </c>
+      <c r="J177" s="16" t="inlineStr">
+        <is>
+          <t>6.74%→5.43%</t>
+        </is>
+      </c>
+      <c r="K177" s="13" t="inlineStr">
+        <is>
+          <t>157→134</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="17" t="n"/>
+      <c r="B178" s="17" t="n"/>
+      <c r="C178" s="17" t="n"/>
+      <c r="D178" s="17" t="n"/>
+      <c r="E178" s="17" t="n"/>
+      <c r="G178" s="14" t="inlineStr">
+        <is>
+          <t>산일전기</t>
+        </is>
+      </c>
+      <c r="H178" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I178" s="15" t="n">
+        <v>-96490800</v>
+      </c>
+      <c r="J178" s="16" t="inlineStr">
+        <is>
+          <t>3.35%→2.71%</t>
+        </is>
+      </c>
+      <c r="K178" s="13" t="inlineStr">
+        <is>
+          <t>239→218</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="17" t="n"/>
+      <c r="B179" s="17" t="n"/>
+      <c r="C179" s="17" t="n"/>
+      <c r="D179" s="17" t="n"/>
+      <c r="E179" s="17" t="n"/>
+      <c r="G179" s="14" t="inlineStr">
+        <is>
+          <t>두산  (편출)</t>
+        </is>
+      </c>
+      <c r="H179" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I179" s="15" t="n">
+        <v>-561792000</v>
+      </c>
+      <c r="J179" s="16" t="inlineStr">
+        <is>
+          <t>1.55%→0.00%</t>
+        </is>
+      </c>
+      <c r="K179" s="13" t="inlineStr">
+        <is>
+          <t>19→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="17" t="n"/>
+      <c r="B180" s="17" t="n"/>
+      <c r="C180" s="17" t="n"/>
+      <c r="D180" s="17" t="n"/>
+      <c r="E180" s="17" t="n"/>
+      <c r="G180" s="14" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H180" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I180" s="15" t="n">
+        <v>-196308000</v>
+      </c>
+      <c r="J180" s="16" t="inlineStr">
+        <is>
+          <t>4.78%→3.90%</t>
+        </is>
+      </c>
+      <c r="K180" s="13" t="inlineStr">
+        <is>
+          <t>150→132</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="17" t="n"/>
+      <c r="B181" s="17" t="n"/>
+      <c r="C181" s="17" t="n"/>
+      <c r="D181" s="17" t="n"/>
+      <c r="E181" s="17" t="n"/>
+      <c r="G181" s="14" t="inlineStr">
+        <is>
+          <t>HD현대일렉트릭  (편출)</t>
+        </is>
+      </c>
+      <c r="H181" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I181" s="15" t="n">
+        <v>-181636000</v>
+      </c>
+      <c r="J181" s="16" t="inlineStr">
+        <is>
+          <t>0.50%→0.00%</t>
+        </is>
+      </c>
+      <c r="K181" s="13" t="inlineStr">
+        <is>
+          <t>13→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="19" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 5종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
+      <c r="E183" s="4" t="n"/>
+      <c r="F183" s="4" t="n"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
+      <c r="K183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H184" s="8" t="n"/>
+      <c r="I184" s="8" t="n"/>
+      <c r="J184" s="8" t="n"/>
+      <c r="K184" s="8" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K185" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
+        <is>
           <t>서진시스템  (신규)</t>
         </is>
       </c>
-      <c r="B160" s="11" t="n">
+      <c r="B186" s="11" t="n">
         <v>314</v>
       </c>
-      <c r="C160" s="11" t="n">
+      <c r="C186" s="11" t="n">
         <v>988362304</v>
       </c>
-      <c r="D160" s="12" t="inlineStr">
+      <c r="D186" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.84%</t>
         </is>
       </c>
-      <c r="E160" s="13" t="inlineStr">
+      <c r="E186" s="13" t="inlineStr">
         <is>
           <t>0→314</t>
         </is>
       </c>
-      <c r="G160" s="14" t="inlineStr">
+      <c r="G186" s="14" t="inlineStr">
         <is>
           <t>기가비스  (편출)</t>
         </is>
       </c>
-      <c r="H160" s="15" t="n">
+      <c r="H186" s="15" t="n">
         <v>-275</v>
       </c>
-      <c r="I160" s="15" t="n">
+      <c r="I186" s="15" t="n">
         <v>-2883568095</v>
       </c>
-      <c r="J160" s="16" t="inlineStr">
+      <c r="J186" s="16" t="inlineStr">
         <is>
           <t>5.28%→0.00%</t>
         </is>
       </c>
-      <c r="K160" s="13" t="inlineStr">
+      <c r="K186" s="13" t="inlineStr">
         <is>
           <t>275→0</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="10" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="10" t="inlineStr">
         <is>
           <t>디케이티  (신규)</t>
         </is>
       </c>
-      <c r="B161" s="11" t="n">
+      <c r="B187" s="11" t="n">
         <v>298</v>
       </c>
-      <c r="C161" s="11" t="n">
+      <c r="C187" s="11" t="n">
         <v>728431350</v>
       </c>
-      <c r="D161" s="12" t="inlineStr">
+      <c r="D187" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.36%</t>
         </is>
       </c>
-      <c r="E161" s="13" t="inlineStr">
+      <c r="E187" s="13" t="inlineStr">
         <is>
           <t>0→298</t>
         </is>
       </c>
-      <c r="G161" s="14" t="inlineStr">
+      <c r="G187" s="14" t="inlineStr">
         <is>
           <t>HPSP  (편출)</t>
         </is>
       </c>
-      <c r="H161" s="15" t="n">
+      <c r="H187" s="15" t="n">
         <v>-203</v>
       </c>
-      <c r="I161" s="15" t="n">
+      <c r="I187" s="15" t="n">
         <v>-931384492</v>
       </c>
-      <c r="J161" s="16" t="inlineStr">
+      <c r="J187" s="16" t="inlineStr">
         <is>
           <t>1.71%→0.00%</t>
         </is>
       </c>
-      <c r="K161" s="13" t="inlineStr">
+      <c r="K187" s="13" t="inlineStr">
         <is>
           <t>203→0</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="10" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
         <is>
           <t>코세스  (신규)</t>
         </is>
       </c>
-      <c r="B162" s="11" t="n">
+      <c r="B188" s="11" t="n">
         <v>268</v>
       </c>
-      <c r="C162" s="11" t="n">
+      <c r="C188" s="11" t="n">
         <v>970950800</v>
       </c>
-      <c r="D162" s="12" t="inlineStr">
+      <c r="D188" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.81%</t>
         </is>
       </c>
-      <c r="E162" s="13" t="inlineStr">
+      <c r="E188" s="13" t="inlineStr">
         <is>
           <t>0→268</t>
         </is>
       </c>
-      <c r="G162" s="14" t="inlineStr">
+      <c r="G188" s="14" t="inlineStr">
         <is>
           <t>인텍플러스</t>
         </is>
       </c>
-      <c r="H162" s="15" t="n">
+      <c r="H188" s="15" t="n">
         <v>-33</v>
       </c>
-      <c r="I162" s="15" t="n">
+      <c r="I188" s="15" t="n">
         <v>-203903742</v>
       </c>
-      <c r="J162" s="16" t="inlineStr">
+      <c r="J188" s="16" t="inlineStr">
         <is>
           <t>9.97%→9.78%</t>
         </is>
       </c>
-      <c r="K162" s="13" t="inlineStr">
+      <c r="K188" s="13" t="inlineStr">
         <is>
           <t>881→848</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="10" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="10" t="inlineStr">
         <is>
           <t>GST  (신규)</t>
         </is>
       </c>
-      <c r="B163" s="11" t="n">
+      <c r="B189" s="11" t="n">
         <v>154</v>
       </c>
-      <c r="C163" s="11" t="n">
+      <c r="C189" s="11" t="n">
         <v>681172940</v>
       </c>
-      <c r="D163" s="12" t="inlineStr">
+      <c r="D189" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.27%</t>
         </is>
       </c>
-      <c r="E163" s="13" t="inlineStr">
+      <c r="E189" s="13" t="inlineStr">
         <is>
           <t>0→154</t>
         </is>
       </c>
-      <c r="G163" s="17" t="n"/>
-      <c r="H163" s="17" t="n"/>
-      <c r="I163" s="17" t="n"/>
-      <c r="J163" s="17" t="n"/>
-      <c r="K163" s="17" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="10" t="inlineStr">
+      <c r="G189" s="17" t="n"/>
+      <c r="H189" s="17" t="n"/>
+      <c r="I189" s="17" t="n"/>
+      <c r="J189" s="17" t="n"/>
+      <c r="K189" s="17" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="B164" s="11" t="n">
+      <c r="B190" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="C164" s="11" t="n">
+      <c r="C190" s="11" t="n">
         <v>580351120</v>
       </c>
-      <c r="D164" s="12" t="inlineStr">
+      <c r="D190" s="12" t="inlineStr">
         <is>
           <t>5.93%→7.13%</t>
         </is>
       </c>
-      <c r="E164" s="13" t="inlineStr">
+      <c r="E190" s="13" t="inlineStr">
         <is>
           <t>173→204</t>
         </is>
       </c>
-      <c r="G164" s="17" t="n"/>
-      <c r="H164" s="17" t="n"/>
-      <c r="I164" s="17" t="n"/>
-      <c r="J164" s="17" t="n"/>
-      <c r="K164" s="17" t="n"/>
-    </row>
-    <row r="166" ht="19" customHeight="1">
-      <c r="A166" s="18" t="inlineStr">
+      <c r="G190" s="17" t="n"/>
+      <c r="H190" s="17" t="n"/>
+      <c r="I190" s="17" t="n"/>
+      <c r="J190" s="17" t="n"/>
+      <c r="K190" s="17" t="n"/>
+    </row>
+    <row r="192" ht="19" customHeight="1">
+      <c r="A192" s="19" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B166" s="19" t="n"/>
-      <c r="C166" s="19" t="n"/>
-      <c r="D166" s="19" t="n"/>
-      <c r="E166" s="19" t="n"/>
-      <c r="F166" s="19" t="n"/>
-      <c r="G166" s="19" t="n"/>
-      <c r="H166" s="19" t="n"/>
-      <c r="I166" s="19" t="n"/>
-      <c r="J166" s="19" t="n"/>
-      <c r="K166" s="19" t="n"/>
-    </row>
-    <row r="168" ht="19" customHeight="1">
-      <c r="A168" s="18" t="inlineStr">
+      <c r="B192" s="20" t="n"/>
+      <c r="C192" s="20" t="n"/>
+      <c r="D192" s="20" t="n"/>
+      <c r="E192" s="20" t="n"/>
+      <c r="F192" s="20" t="n"/>
+      <c r="G192" s="20" t="n"/>
+      <c r="H192" s="20" t="n"/>
+      <c r="I192" s="20" t="n"/>
+      <c r="J192" s="20" t="n"/>
+      <c r="K192" s="20" t="n"/>
+    </row>
+    <row r="194" ht="19" customHeight="1">
+      <c r="A194" s="19" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B168" s="19" t="n"/>
-      <c r="C168" s="19" t="n"/>
-      <c r="D168" s="19" t="n"/>
-      <c r="E168" s="19" t="n"/>
-      <c r="F168" s="19" t="n"/>
-      <c r="G168" s="19" t="n"/>
-      <c r="H168" s="19" t="n"/>
-      <c r="I168" s="19" t="n"/>
-      <c r="J168" s="19" t="n"/>
-      <c r="K168" s="19" t="n"/>
-    </row>
-    <row r="170" ht="19" customHeight="1">
-      <c r="A170" s="18" t="inlineStr">
+      <c r="B194" s="20" t="n"/>
+      <c r="C194" s="20" t="n"/>
+      <c r="D194" s="20" t="n"/>
+      <c r="E194" s="20" t="n"/>
+      <c r="F194" s="20" t="n"/>
+      <c r="G194" s="20" t="n"/>
+      <c r="H194" s="20" t="n"/>
+      <c r="I194" s="20" t="n"/>
+      <c r="J194" s="20" t="n"/>
+      <c r="K194" s="20" t="n"/>
+    </row>
+    <row r="196" ht="19" customHeight="1">
+      <c r="A196" s="19" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B170" s="19" t="n"/>
-      <c r="C170" s="19" t="n"/>
-      <c r="D170" s="19" t="n"/>
-      <c r="E170" s="19" t="n"/>
-      <c r="F170" s="19" t="n"/>
-      <c r="G170" s="19" t="n"/>
-      <c r="H170" s="19" t="n"/>
-      <c r="I170" s="19" t="n"/>
-      <c r="J170" s="19" t="n"/>
-      <c r="K170" s="19" t="n"/>
-    </row>
-    <row r="172" ht="19" customHeight="1">
-      <c r="A172" s="3" t="inlineStr">
+      <c r="B196" s="20" t="n"/>
+      <c r="C196" s="20" t="n"/>
+      <c r="D196" s="20" t="n"/>
+      <c r="E196" s="20" t="n"/>
+      <c r="F196" s="20" t="n"/>
+      <c r="G196" s="20" t="n"/>
+      <c r="H196" s="20" t="n"/>
+      <c r="I196" s="20" t="n"/>
+      <c r="J196" s="20" t="n"/>
+      <c r="K196" s="20" t="n"/>
+    </row>
+    <row r="198" ht="19" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B172" s="4" t="n"/>
-      <c r="C172" s="4" t="n"/>
-      <c r="D172" s="4" t="n"/>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="n"/>
-      <c r="G172" s="4" t="n"/>
-      <c r="H172" s="4" t="n"/>
-      <c r="I172" s="4" t="n"/>
-      <c r="J172" s="4" t="n"/>
-      <c r="K172" s="4" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="20" t="inlineStr">
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="4" t="n"/>
+      <c r="D198" s="4" t="n"/>
+      <c r="E198" s="4" t="n"/>
+      <c r="F198" s="4" t="n"/>
+      <c r="G198" s="4" t="n"/>
+      <c r="H198" s="4" t="n"/>
+      <c r="I198" s="4" t="n"/>
+      <c r="J198" s="4" t="n"/>
+      <c r="K198" s="4" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="19" customHeight="1">
-      <c r="A175" s="3" t="inlineStr">
+    <row r="201" ht="19" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B175" s="4" t="n"/>
-      <c r="C175" s="4" t="n"/>
-      <c r="D175" s="4" t="n"/>
-      <c r="E175" s="4" t="n"/>
-      <c r="F175" s="4" t="n"/>
-      <c r="G175" s="4" t="n"/>
-      <c r="H175" s="4" t="n"/>
-      <c r="I175" s="4" t="n"/>
-      <c r="J175" s="4" t="n"/>
-      <c r="K175" s="4" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="20" t="inlineStr">
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
+      <c r="E201" s="4" t="n"/>
+      <c r="F201" s="4" t="n"/>
+      <c r="G201" s="4" t="n"/>
+      <c r="H201" s="4" t="n"/>
+      <c r="I201" s="4" t="n"/>
+      <c r="J201" s="4" t="n"/>
+      <c r="K201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="19" customHeight="1">
-      <c r="A178" s="3" t="inlineStr">
+    <row r="204" ht="19" customHeight="1">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.3%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="n"/>
+      <c r="C204" s="4" t="n"/>
+      <c r="D204" s="4" t="n"/>
+      <c r="E204" s="4" t="n"/>
+      <c r="F204" s="4" t="n"/>
+      <c r="G204" s="4" t="n"/>
+      <c r="H204" s="4" t="n"/>
+      <c r="I204" s="4" t="n"/>
+      <c r="J204" s="4" t="n"/>
+      <c r="K204" s="4" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="19" customHeight="1">
+      <c r="A207" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
-      <c r="B178" s="4" t="n"/>
-      <c r="C178" s="4" t="n"/>
-      <c r="D178" s="4" t="n"/>
-      <c r="E178" s="4" t="n"/>
-      <c r="F178" s="4" t="n"/>
-      <c r="G178" s="4" t="n"/>
-      <c r="H178" s="4" t="n"/>
-      <c r="I178" s="4" t="n"/>
-      <c r="J178" s="4" t="n"/>
-      <c r="K178" s="4" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr">
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="4" t="n"/>
+      <c r="D207" s="4" t="n"/>
+      <c r="E207" s="4" t="n"/>
+      <c r="F207" s="4" t="n"/>
+      <c r="G207" s="4" t="n"/>
+      <c r="H207" s="4" t="n"/>
+      <c r="I207" s="4" t="n"/>
+      <c r="J207" s="4" t="n"/>
+      <c r="K207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B179" s="6" t="n"/>
-      <c r="C179" s="6" t="n"/>
-      <c r="D179" s="6" t="n"/>
-      <c r="E179" s="6" t="n"/>
-      <c r="G179" s="7" t="inlineStr">
+      <c r="B208" s="6" t="n"/>
+      <c r="C208" s="6" t="n"/>
+      <c r="D208" s="6" t="n"/>
+      <c r="E208" s="6" t="n"/>
+      <c r="G208" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H179" s="8" t="n"/>
-      <c r="I179" s="8" t="n"/>
-      <c r="J179" s="8" t="n"/>
-      <c r="K179" s="8" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="9" t="inlineStr">
+      <c r="H208" s="8" t="n"/>
+      <c r="I208" s="8" t="n"/>
+      <c r="J208" s="8" t="n"/>
+      <c r="K208" s="8" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B180" s="9" t="inlineStr">
+      <c r="B209" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C180" s="9" t="inlineStr">
+      <c r="C209" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D180" s="9" t="inlineStr">
+      <c r="D209" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E180" s="9" t="inlineStr">
+      <c r="E209" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G180" s="9" t="inlineStr">
+      <c r="G209" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H180" s="9" t="inlineStr">
+      <c r="H209" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I180" s="9" t="inlineStr">
+      <c r="I209" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J180" s="9" t="inlineStr">
+      <c r="J209" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K180" s="9" t="inlineStr">
+      <c r="K209" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="10" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
         <is>
           <t>큐리언트  (신규)</t>
         </is>
       </c>
-      <c r="B181" s="11" t="n">
+      <c r="B210" s="11" t="n">
         <v>176</v>
       </c>
-      <c r="C181" s="11" t="n">
+      <c r="C210" s="11" t="n">
         <v>25301760</v>
       </c>
-      <c r="D181" s="12" t="inlineStr">
+      <c r="D210" s="12" t="inlineStr">
         <is>
           <t>0.00%→0.43%</t>
         </is>
       </c>
-      <c r="E181" s="13" t="inlineStr">
+      <c r="E210" s="13" t="inlineStr">
         <is>
           <t>0→176</t>
         </is>
       </c>
-      <c r="G181" s="14" t="inlineStr">
+      <c r="G210" s="14" t="inlineStr">
         <is>
           <t>엘티씨</t>
         </is>
       </c>
-      <c r="H181" s="15" t="n">
+      <c r="H210" s="15" t="n">
         <v>-98</v>
       </c>
-      <c r="I181" s="15" t="n">
+      <c r="I210" s="15" t="n">
         <v>-32026400</v>
       </c>
-      <c r="J181" s="16" t="inlineStr">
+      <c r="J210" s="16" t="inlineStr">
         <is>
           <t>3.84%→3.28%</t>
         </is>
       </c>
-      <c r="K181" s="13" t="inlineStr">
+      <c r="K210" s="13" t="inlineStr">
         <is>
           <t>683→585</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="10" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="10" t="inlineStr">
         <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="B182" s="11" t="n">
+      <c r="B211" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="C182" s="11" t="n">
+      <c r="C211" s="11" t="n">
         <v>22848000</v>
       </c>
-      <c r="D182" s="12" t="inlineStr">
+      <c r="D211" s="12" t="inlineStr">
         <is>
           <t>3.15%→3.54%</t>
         </is>
       </c>
-      <c r="E182" s="13" t="inlineStr">
+      <c r="E211" s="13" t="inlineStr">
         <is>
           <t>449→505</t>
         </is>
       </c>
-      <c r="G182" s="14" t="inlineStr">
+      <c r="G211" s="14" t="inlineStr">
         <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H182" s="15" t="n">
+      <c r="H211" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I182" s="15" t="n">
+      <c r="I211" s="15" t="n">
         <v>-26633600</v>
       </c>
-      <c r="J182" s="16" t="inlineStr">
+      <c r="J211" s="16" t="inlineStr">
         <is>
           <t>4.53%→4.07%</t>
         </is>
       </c>
-      <c r="K182" s="13" t="inlineStr">
+      <c r="K211" s="13" t="inlineStr">
         <is>
           <t>277→249</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="10" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
         <is>
           <t>대주전자재료</t>
         </is>
       </c>
-      <c r="B183" s="11" t="n">
+      <c r="B212" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C183" s="11" t="n">
+      <c r="C212" s="11" t="n">
         <v>9379200</v>
       </c>
-      <c r="D183" s="12" t="inlineStr">
+      <c r="D212" s="12" t="inlineStr">
         <is>
           <t>2.38%→2.54%</t>
         </is>
       </c>
-      <c r="E183" s="13" t="inlineStr">
+      <c r="E212" s="13" t="inlineStr">
         <is>
           <t>177→189</t>
         </is>
       </c>
-      <c r="G183" s="14" t="inlineStr">
+      <c r="G212" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H183" s="15" t="n">
+      <c r="H212" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I183" s="15" t="n">
+      <c r="I212" s="15" t="n">
         <v>-29336000</v>
       </c>
-      <c r="J183" s="16" t="inlineStr">
+      <c r="J212" s="16" t="inlineStr">
         <is>
           <t>5.36%→4.85%</t>
         </is>
       </c>
-      <c r="K183" s="13" t="inlineStr">
+      <c r="K212" s="13" t="inlineStr">
         <is>
           <t>202→183</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="10" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="B184" s="11" t="n">
+      <c r="B213" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C184" s="11" t="n">
+      <c r="C213" s="11" t="n">
         <v>36828000</v>
       </c>
-      <c r="D184" s="12" t="inlineStr">
+      <c r="D213" s="12" t="inlineStr">
         <is>
           <t>5.81%→6.44%</t>
         </is>
       </c>
-      <c r="E184" s="13" t="inlineStr">
+      <c r="E213" s="13" t="inlineStr">
         <is>
           <t>101→112</t>
         </is>
       </c>
-      <c r="G184" s="17" t="n"/>
-      <c r="H184" s="17" t="n"/>
-      <c r="I184" s="17" t="n"/>
-      <c r="J184" s="17" t="n"/>
-      <c r="K184" s="17" t="n"/>
+      <c r="G213" s="17" t="n"/>
+      <c r="H213" s="17" t="n"/>
+      <c r="I213" s="17" t="n"/>
+      <c r="J213" s="17" t="n"/>
+      <c r="K213" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A176:K176"/>
-    <mergeCell ref="G158:K158"/>
+  <mergeCells count="57">
     <mergeCell ref="G105:K105"/>
-    <mergeCell ref="A157:K157"/>
-    <mergeCell ref="A166:K166"/>
+    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A201:K201"/>
+    <mergeCell ref="G208:K208"/>
     <mergeCell ref="G86:K86"/>
     <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A178:K178"/>
+    <mergeCell ref="A142:K142"/>
     <mergeCell ref="G98:K98"/>
     <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A207:K207"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G179:K179"/>
-    <mergeCell ref="A168:K168"/>
+    <mergeCell ref="G157:K157"/>
+    <mergeCell ref="A162:K162"/>
+    <mergeCell ref="A205:K205"/>
     <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A172:K172"/>
+    <mergeCell ref="A196:K196"/>
     <mergeCell ref="G66:K66"/>
+    <mergeCell ref="A183:K183"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A208:E208"/>
     <mergeCell ref="A66:E66"/>
+    <mergeCell ref="G184:K184"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="A120:K120"/>
-    <mergeCell ref="A158:E158"/>
     <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A149:K149"/>
-    <mergeCell ref="G152:K152"/>
+    <mergeCell ref="A192:K192"/>
+    <mergeCell ref="A198:K198"/>
+    <mergeCell ref="A163:E163"/>
     <mergeCell ref="G121:K121"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A139:K139"/>
     <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A179:E179"/>
+    <mergeCell ref="A154:K154"/>
     <mergeCell ref="A104:K104"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A204:K204"/>
     <mergeCell ref="A85:K85"/>
-    <mergeCell ref="A175:K175"/>
-    <mergeCell ref="A151:K151"/>
+    <mergeCell ref="A194:K194"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="G163:K163"/>
+    <mergeCell ref="A184:E184"/>
     <mergeCell ref="A97:K97"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G76:K76"/>
-    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="G143:K143"/>
+    <mergeCell ref="A156:K156"/>
+    <mergeCell ref="A152:K152"/>
     <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A170:K170"/>
-    <mergeCell ref="G140:K140"/>
-    <mergeCell ref="A173:K173"/>
+    <mergeCell ref="A199:K199"/>
+    <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A202:K202"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261029.xlsx
+++ b/reports/pdf_rolling5_20261029.xlsx
@@ -2422,23 +2422,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-820410246</v>
+        <v>-3518426055</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.88%</t>
+          <t>2.85%→1.26%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>300→250</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -2466,23 +2466,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-3518426055</v>
+        <v>-820410246</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.85%→1.26%</t>
+          <t>1.97%→1.88%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>300→250</t>
         </is>
       </c>
     </row>
@@ -2686,23 +2686,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1629147988</v>
+        <v>-1103885331</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.58%→0.75%</t>
+          <t>1.22%→0.71%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2714,23 +2714,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1103885331</v>
+        <v>-1629147988</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.22%→0.71%</t>
+          <t>1.58%→0.75%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2770,23 +2770,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>파크시스템스  (편출)</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-5303652090</v>
+        <v>-3180923954</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>3.68%→1.41%</t>
+          <t>1.36%→0.00%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
@@ -2798,23 +2798,23 @@
       <c r="E62" s="17" t="n"/>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스  (편출)</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-3180923954</v>
+        <v>-5303652090</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.36%→0.00%</t>
+          <t>3.68%→1.41%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -3974,23 +3974,23 @@
       <c r="E101" s="17" t="n"/>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H101" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>-78199886</v>
+        <v>-551313362</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.22%</t>
+          <t>7.68%→5.13%</t>
         </is>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -4002,23 +4002,23 @@
       <c r="E102" s="17" t="n"/>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H102" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I102" s="15" t="n">
-        <v>-551313362</v>
+        <v>-78199886</v>
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>7.68%→5.13%</t>
+          <t>0.41%→0.22%</t>
         </is>
       </c>
       <c r="K102" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -4399,23 +4399,23 @@
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>프로텍</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-1121999604</v>
+        <v>-267239906</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2.40%→1.13%</t>
+          <t>0.71%→0.40%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>46→22</t>
+          <t>57→33</t>
         </is>
       </c>
     </row>
@@ -4443,23 +4443,23 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-267239906</v>
+        <v>-1121999604</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.40%</t>
+          <t>2.40%→1.13%</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>57→33</t>
+          <t>46→22</t>
         </is>
       </c>
     </row>
@@ -5176,23 +5176,23 @@
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-311708326</v>
+        <v>-136656568</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>1.71%→0.68%</t>
+          <t>1.95%→1.48%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>10→4</t>
+          <t>26→20</t>
         </is>
       </c>
     </row>
@@ -5220,46 +5220,46 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>태성</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H134" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I134" s="15" t="n">
-        <v>-136656568</v>
+        <v>-311708326</v>
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>1.95%→1.48%</t>
+          <t>1.71%→0.68%</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>26→20</t>
+          <t>10→4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B135" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>43952390</v>
+        <v>11366997</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.95%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
@@ -5287,23 +5287,23 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>11366997</v>
+        <v>43952390</v>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.82%→0.95%</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
@@ -5359,7 +5359,7 @@
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 21억(0.5%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B139" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
     <row r="162" ht="19" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 5억(1.4%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 12종목  /  매도 17종목</t>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 12종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B162" s="4" t="n"/>
@@ -7080,7 +7080,7 @@
     <row r="204" ht="19" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.3%)      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억      오늘 2026-10-29  vs  5일전 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B204" s="4" t="n"/>
